--- a/Manual Trading/Day 2/optimal_allocation.xlsx
+++ b/Manual Trading/Day 2/optimal_allocation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92c4f7ffed9c6980/Python/IntaraTradingAlgorithm/Manual Trading/Day 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="11_3C91D1A4D360D04F55E2DCF0505ED87656CD3EF8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{944728CE-1BE6-43D9-A2C8-E1263E8FF1E2}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="11_3C91D1A4D360D04F55E2DCF0505ED87656CD3EF8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CAD003B-9C92-4598-A270-820A1D908EF8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Allocation</t>
   </si>
@@ -76,6 +76,12 @@
   <si>
     <t>normally distributed + 5 to capture excess scale not being used by others</t>
   </si>
+  <si>
+    <t>cumulative quantity</t>
+  </si>
+  <si>
+    <t>quantity at this price</t>
+  </si>
 </sst>
 </file>
 
@@ -110,8 +116,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R104"/>
+  <dimension ref="A1:T106"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="52.7265625" customWidth="1"/>
@@ -425,9 +432,12 @@
     <col min="16" max="16" width="31.26953125" customWidth="1"/>
     <col min="17" max="17" width="43.36328125" customWidth="1"/>
     <col min="18" max="18" width="60.453125" customWidth="1"/>
+    <col min="19" max="19" width="30.36328125" customWidth="1"/>
+    <col min="20" max="20" width="24.7265625" customWidth="1"/>
+    <col min="21" max="21" width="17.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -464,8 +474,14 @@
       <c r="R1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -498,8 +514,16 @@
         <f>0.5</f>
         <v>0.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S2">
+        <f>(0.3*N2+0.18*O2+0.02*P2+0.3*Q2+0.2*R2)*5000</f>
+        <v>464.85148514851483</v>
+      </c>
+      <c r="T2">
+        <f>SUM($S$2:S2)</f>
+        <v>464.85148514851483</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -531,8 +555,16 @@
       <c r="O3">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S3">
+        <f t="shared" ref="S3:S66" si="4">(0.3*N3+0.18*O3+0.02*P3+0.3*Q3+0.2*R3)*5000</f>
+        <v>464.85148514851483</v>
+      </c>
+      <c r="T3">
+        <f>SUM($S$2:S3)</f>
+        <v>929.70297029702965</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -561,8 +593,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S4">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T4">
+        <f>SUM($S$2:S4)</f>
+        <v>944.55445544554448</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -591,8 +631,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S5">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T5">
+        <f>SUM($S$2:S5)</f>
+        <v>959.4059405940593</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -621,8 +669,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S6">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T6">
+        <f>SUM($S$2:S6)</f>
+        <v>974.25742574257413</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -651,8 +707,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S7">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T7">
+        <f>SUM($S$2:S7)</f>
+        <v>989.10891089108895</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -681,8 +745,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S8">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T8">
+        <f>SUM($S$2:S8)</f>
+        <v>1003.9603960396038</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -711,8 +783,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S9">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T9">
+        <f>SUM($S$2:S9)</f>
+        <v>1018.8118811881186</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -741,8 +821,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S10">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T10">
+        <f>SUM($S$2:S10)</f>
+        <v>1033.6633663366335</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -771,8 +859,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S11">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T11">
+        <f>SUM($S$2:S11)</f>
+        <v>1048.5148514851485</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -801,8 +897,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S12">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T12">
+        <f>SUM($S$2:S12)</f>
+        <v>1063.3663366336634</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -831,8 +935,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S13">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T13">
+        <f>SUM($S$2:S13)</f>
+        <v>1078.2178217821784</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -861,8 +973,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S14">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T14">
+        <f>SUM($S$2:S14)</f>
+        <v>1093.0693069306933</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -891,8 +1011,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S15">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T15">
+        <f>SUM($S$2:S15)</f>
+        <v>1107.9207920792082</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -921,8 +1049,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S16">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T16">
+        <f>SUM($S$2:S16)</f>
+        <v>1122.7722772277232</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
@@ -951,8 +1087,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S17">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T17">
+        <f>SUM($S$2:S17)</f>
+        <v>1137.6237623762381</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
@@ -981,8 +1125,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S18">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T18">
+        <f>SUM($S$2:S18)</f>
+        <v>1152.4752475247531</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1011,8 +1163,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S19">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T19">
+        <f>SUM($S$2:S19)</f>
+        <v>1167.326732673268</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1041,8 +1201,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S20">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T20">
+        <f>SUM($S$2:S20)</f>
+        <v>1182.1782178217829</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1071,8 +1239,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S21">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T21">
+        <f>SUM($S$2:S21)</f>
+        <v>1197.0297029702979</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1101,8 +1277,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S22">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T22">
+        <f>SUM($S$2:S22)</f>
+        <v>1211.8811881188128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1131,8 +1315,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S23">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T23">
+        <f>SUM($S$2:S23)</f>
+        <v>1226.7326732673278</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1161,8 +1353,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S24">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T24">
+        <f>SUM($S$2:S24)</f>
+        <v>1241.5841584158427</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1191,8 +1391,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S25">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T25">
+        <f>SUM($S$2:S25)</f>
+        <v>1256.4356435643576</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1221,8 +1429,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S26">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T26">
+        <f>SUM($S$2:S26)</f>
+        <v>1271.2871287128726</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1251,8 +1467,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S27">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T27">
+        <f>SUM($S$2:S27)</f>
+        <v>1286.1386138613875</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1281,8 +1505,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S28">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T28">
+        <f>SUM($S$2:S28)</f>
+        <v>1300.9900990099025</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1311,8 +1543,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S29">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T29">
+        <f>SUM($S$2:S29)</f>
+        <v>1315.8415841584174</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1341,8 +1581,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S30">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T30">
+        <f>SUM($S$2:S30)</f>
+        <v>1330.6930693069323</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1371,8 +1619,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S31">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T31">
+        <f>SUM($S$2:S31)</f>
+        <v>1345.5445544554473</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>30</v>
       </c>
@@ -1401,8 +1657,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S32">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T32">
+        <f>SUM($S$2:S32)</f>
+        <v>1360.3960396039622</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>31</v>
       </c>
@@ -1431,8 +1695,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S33">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T33">
+        <f>SUM($S$2:S33)</f>
+        <v>1375.2475247524771</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>32</v>
       </c>
@@ -1461,8 +1733,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S34">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T34">
+        <f>SUM($S$2:S34)</f>
+        <v>1390.0990099009921</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>33</v>
       </c>
@@ -1491,8 +1771,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S35">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T35">
+        <f>SUM($S$2:S35)</f>
+        <v>1404.950495049507</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>34</v>
       </c>
@@ -1521,8 +1809,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S36">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T36">
+        <f>SUM($S$2:S36)</f>
+        <v>1419.801980198022</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1551,8 +1847,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S37">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T37">
+        <f>SUM($S$2:S37)</f>
+        <v>1434.6534653465369</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1581,8 +1885,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S38">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T38">
+        <f>SUM($S$2:S38)</f>
+        <v>1449.5049504950518</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>37</v>
       </c>
@@ -1611,8 +1923,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S39">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T39">
+        <f>SUM($S$2:S39)</f>
+        <v>1464.3564356435668</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1641,8 +1961,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S40">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T40">
+        <f>SUM($S$2:S40)</f>
+        <v>1479.2079207920817</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>39</v>
       </c>
@@ -1671,8 +1999,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S41">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T41">
+        <f>SUM($S$2:S41)</f>
+        <v>1494.0594059405967</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>40</v>
       </c>
@@ -1701,8 +2037,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S42">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T42">
+        <f>SUM($S$2:S42)</f>
+        <v>1508.9108910891116</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>41</v>
       </c>
@@ -1731,8 +2075,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S43">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T43">
+        <f>SUM($S$2:S43)</f>
+        <v>1523.7623762376265</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>42</v>
       </c>
@@ -1761,8 +2113,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S44">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T44">
+        <f>SUM($S$2:S44)</f>
+        <v>1538.6138613861415</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>43</v>
       </c>
@@ -1791,8 +2151,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S45">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T45">
+        <f>SUM($S$2:S45)</f>
+        <v>1553.4653465346564</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>44</v>
       </c>
@@ -1821,8 +2189,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S46">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T46">
+        <f>SUM($S$2:S46)</f>
+        <v>1568.3168316831714</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>45</v>
       </c>
@@ -1851,8 +2227,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S47">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T47">
+        <f>SUM($S$2:S47)</f>
+        <v>1583.1683168316863</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>46</v>
       </c>
@@ -1881,8 +2265,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S48">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T48">
+        <f>SUM($S$2:S48)</f>
+        <v>1598.0198019802012</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>47</v>
       </c>
@@ -1911,8 +2303,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S49">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T49">
+        <f>SUM($S$2:S49)</f>
+        <v>1612.8712871287162</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>48</v>
       </c>
@@ -1941,8 +2341,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S50">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T50">
+        <f>SUM($S$2:S50)</f>
+        <v>1627.7227722772311</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>49</v>
       </c>
@@ -1971,8 +2379,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S51">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T51">
+        <f>SUM($S$2:S51)</f>
+        <v>1642.5742574257461</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>50</v>
       </c>
@@ -2001,8 +2417,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S52">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T52">
+        <f>SUM($S$2:S52)</f>
+        <v>1657.425742574261</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>51</v>
       </c>
@@ -2031,8 +2455,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S53">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T53">
+        <f>SUM($S$2:S53)</f>
+        <v>1672.2772277227759</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>52</v>
       </c>
@@ -2061,8 +2493,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S54">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T54">
+        <f>SUM($S$2:S54)</f>
+        <v>1687.1287128712909</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>53</v>
       </c>
@@ -2091,8 +2531,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S55">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T55">
+        <f>SUM($S$2:S55)</f>
+        <v>1701.9801980198058</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>54</v>
       </c>
@@ -2121,8 +2569,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S56">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T56">
+        <f>SUM($S$2:S56)</f>
+        <v>1716.8316831683208</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>55</v>
       </c>
@@ -2151,8 +2607,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S57">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T57">
+        <f>SUM($S$2:S57)</f>
+        <v>1731.6831683168357</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>56</v>
       </c>
@@ -2181,8 +2645,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S58">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T58">
+        <f>SUM($S$2:S58)</f>
+        <v>1746.5346534653506</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>57</v>
       </c>
@@ -2211,8 +2683,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S59">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T59">
+        <f>SUM($S$2:S59)</f>
+        <v>1761.3861386138656</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>58</v>
       </c>
@@ -2241,8 +2721,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S60">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T60">
+        <f>SUM($S$2:S60)</f>
+        <v>1776.2376237623805</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>59</v>
       </c>
@@ -2271,8 +2759,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S61">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T61">
+        <f>SUM($S$2:S61)</f>
+        <v>1791.0891089108954</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>60</v>
       </c>
@@ -2301,8 +2797,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S62">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T62">
+        <f>SUM($S$2:S62)</f>
+        <v>1805.9405940594104</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>61</v>
       </c>
@@ -2331,8 +2835,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S63">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T63">
+        <f>SUM($S$2:S63)</f>
+        <v>1820.7920792079253</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>62</v>
       </c>
@@ -2361,8 +2873,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S64">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T64">
+        <f>SUM($S$2:S64)</f>
+        <v>1835.6435643564403</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>63</v>
       </c>
@@ -2391,8 +2911,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S65">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T65">
+        <f>SUM($S$2:S65)</f>
+        <v>1850.4950495049552</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>64</v>
       </c>
@@ -2421,8 +2949,16 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S66">
+        <f t="shared" si="4"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T66">
+        <f>SUM($S$2:S66)</f>
+        <v>1865.3465346534701</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>65</v>
       </c>
@@ -2433,26 +2969,34 @@
         <v>42113.404123037239</v>
       </c>
       <c r="D67">
-        <f t="shared" ref="D67:D102" si="4">100-A67</f>
+        <f t="shared" ref="D67:D102" si="5">100-A67</f>
         <v>35</v>
       </c>
       <c r="E67">
-        <f t="shared" ref="E67:E102" si="5">D67*0.08+1</f>
+        <f t="shared" ref="E67:E102" si="6">D67*0.08+1</f>
         <v>3.8000000000000003</v>
       </c>
       <c r="F67">
-        <f t="shared" ref="F67:F103" si="6">E67*C67</f>
+        <f t="shared" ref="F67:F103" si="7">E67*C67</f>
         <v>160030.93566754152</v>
       </c>
       <c r="M67">
         <v>65</v>
       </c>
       <c r="N67">
-        <f t="shared" ref="N67:N104" si="7">1/101</f>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+        <f t="shared" ref="N67:N104" si="8">1/101</f>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S67">
+        <f t="shared" ref="S67:S105" si="9">(0.3*N67+0.18*O67+0.02*P67+0.3*Q67+0.2*R67)*5000</f>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T67">
+        <f>SUM($S$2:S67)</f>
+        <v>1880.1980198019851</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>66</v>
       </c>
@@ -2463,26 +3007,34 @@
         <v>42972.861350038002</v>
       </c>
       <c r="D68">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>34</v>
       </c>
       <c r="E68">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.72</v>
       </c>
       <c r="F68">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>159859.04422214138</v>
       </c>
       <c r="M68">
         <v>66</v>
       </c>
       <c r="N68">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S68">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T68">
+        <f>SUM($S$2:S68)</f>
+        <v>1895.0495049505</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>67</v>
       </c>
@@ -2493,26 +3045,34 @@
         <v>43839.813568121113</v>
       </c>
       <c r="D69">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>33</v>
       </c>
       <c r="E69">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.64</v>
       </c>
       <c r="F69">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>159576.92138796087</v>
       </c>
       <c r="M69">
         <v>67</v>
       </c>
       <c r="N69">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S69">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T69">
+        <f>SUM($S$2:S69)</f>
+        <v>1909.900990099015</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>68</v>
       </c>
@@ -2523,26 +3083,34 @@
         <v>44716.609839483528</v>
       </c>
       <c r="D70">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>32</v>
       </c>
       <c r="E70">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.56</v>
       </c>
       <c r="F70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>159191.13102856136</v>
       </c>
       <c r="M70">
         <v>68</v>
       </c>
       <c r="N70">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S70">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T70">
+        <f>SUM($S$2:S70)</f>
+        <v>1924.7524752475299</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>69</v>
       </c>
@@ -2553,26 +3121,34 @@
         <v>45593.406110845957</v>
       </c>
       <c r="D71">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>31</v>
       </c>
       <c r="E71">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.48</v>
       </c>
       <c r="F71">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>158665.05326574392</v>
       </c>
       <c r="M71">
         <v>69</v>
       </c>
       <c r="N71">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S71">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T71">
+        <f>SUM($S$2:S71)</f>
+        <v>1939.6039603960448</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>70</v>
       </c>
@@ -2583,26 +3159,34 @@
         <v>46470.202382208372</v>
       </c>
       <c r="D72">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="E72">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.4</v>
       </c>
       <c r="F72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>157998.68809950846</v>
       </c>
       <c r="M72">
         <v>70</v>
       </c>
       <c r="N72">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S72">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T72">
+        <f>SUM($S$2:S72)</f>
+        <v>1954.4554455445598</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>71</v>
       </c>
@@ -2613,26 +3197,34 @@
         <v>47346.998653570801</v>
       </c>
       <c r="D73">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="E73">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.32</v>
       </c>
       <c r="F73">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>157192.03552985506</v>
       </c>
       <c r="M73">
         <v>71</v>
       </c>
       <c r="N73">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S73">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T73">
+        <f>SUM($S$2:S73)</f>
+        <v>1969.3069306930747</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>72</v>
       </c>
@@ -2643,26 +3235,34 @@
         <v>48232.670417312831</v>
       </c>
       <c r="D74">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>28</v>
       </c>
       <c r="E74">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.24</v>
       </c>
       <c r="F74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>156273.85215209358</v>
       </c>
       <c r="M74">
         <v>72</v>
       </c>
       <c r="N74">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S74">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T74">
+        <f>SUM($S$2:S74)</f>
+        <v>1984.1584158415897</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>73</v>
       </c>
@@ -2673,26 +3273,34 @@
         <v>49125.868017633453</v>
       </c>
       <c r="D75">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="E75">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.16</v>
       </c>
       <c r="F75">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>155237.7429357217</v>
       </c>
       <c r="M75">
         <v>73</v>
       </c>
       <c r="N75">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S75">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T75">
+        <f>SUM($S$2:S75)</f>
+        <v>1999.0099009901046</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>74</v>
       </c>
@@ -2703,26 +3311,34 @@
         <v>50019.065617954053</v>
       </c>
       <c r="D76">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>26</v>
       </c>
       <c r="E76">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.08</v>
       </c>
       <c r="F76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>154058.7221032985</v>
       </c>
       <c r="M76">
         <v>74</v>
       </c>
       <c r="N76">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S76">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T76">
+        <f>SUM($S$2:S76)</f>
+        <v>2013.8613861386195</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>75</v>
       </c>
@@ -2733,686 +3349,870 @@
         <v>50912.26321827466</v>
       </c>
       <c r="D77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="E77">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="F77">
+        <f t="shared" si="7"/>
+        <v>152736.78965482398</v>
+      </c>
+      <c r="M77">
+        <v>75</v>
+      </c>
+      <c r="N77">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S77">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T77">
+        <f>SUM($S$2:S77)</f>
+        <v>2028.7128712871345</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="B78">
+        <v>18</v>
+      </c>
+      <c r="C78">
+        <v>51805.460818595267</v>
+      </c>
+      <c r="D78">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="E78">
+        <f t="shared" si="6"/>
+        <v>2.92</v>
+      </c>
+      <c r="F78">
+        <f t="shared" si="7"/>
+        <v>151271.94559029819</v>
+      </c>
+      <c r="M78">
+        <v>76</v>
+      </c>
+      <c r="N78">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S78">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T78">
+        <f>SUM($S$2:S78)</f>
+        <v>2043.5643564356494</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="B79">
+        <v>19</v>
+      </c>
+      <c r="C79">
+        <v>52707.932485168298</v>
+      </c>
+      <c r="D79">
+        <f t="shared" si="5"/>
+        <v>23</v>
+      </c>
+      <c r="E79">
+        <f t="shared" si="6"/>
+        <v>2.84</v>
+      </c>
+      <c r="F79">
+        <f t="shared" si="7"/>
+        <v>149690.52825787794</v>
+      </c>
+      <c r="M79">
+        <v>77</v>
+      </c>
+      <c r="N79">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S79">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T79">
+        <f>SUM($S$2:S79)</f>
+        <v>2058.4158415841644</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="B80">
+        <v>19</v>
+      </c>
+      <c r="C80">
+        <v>53616.689941809127</v>
+      </c>
+      <c r="D80">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
+      <c r="E80">
+        <f t="shared" si="6"/>
+        <v>2.76</v>
+      </c>
+      <c r="F80">
+        <f t="shared" si="7"/>
+        <v>147982.06423939319</v>
+      </c>
+      <c r="M80">
+        <v>78</v>
+      </c>
+      <c r="N80">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S80">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T80">
+        <f>SUM($S$2:S80)</f>
+        <v>2073.2673267326791</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="B81">
+        <v>19</v>
+      </c>
+      <c r="C81">
+        <v>54525.447398449956</v>
+      </c>
+      <c r="D81">
+        <f t="shared" si="5"/>
+        <v>21</v>
+      </c>
+      <c r="E81">
+        <f t="shared" si="6"/>
+        <v>2.6799999999999997</v>
+      </c>
+      <c r="F81">
+        <f t="shared" si="7"/>
+        <v>146128.19902784587</v>
+      </c>
+      <c r="M81">
+        <v>79</v>
+      </c>
+      <c r="N81">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S81">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T81">
+        <f>SUM($S$2:S81)</f>
+        <v>2088.1188118811938</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="B82">
+        <v>19</v>
+      </c>
+      <c r="C82">
+        <v>55434.204855090793</v>
+      </c>
+      <c r="D82">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="E82">
+        <f t="shared" si="6"/>
+        <v>2.6</v>
+      </c>
+      <c r="F82">
+        <f t="shared" si="7"/>
+        <v>144128.93262323606</v>
+      </c>
+      <c r="M82">
+        <v>80</v>
+      </c>
+      <c r="N82">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S82">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T82">
+        <f>SUM($S$2:S82)</f>
+        <v>2102.9702970297085</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="B83">
+        <v>19</v>
+      </c>
+      <c r="C83">
+        <v>56342.96231173163</v>
+      </c>
+      <c r="D83">
+        <f t="shared" si="5"/>
+        <v>19</v>
+      </c>
+      <c r="E83">
+        <f t="shared" si="6"/>
+        <v>2.52</v>
+      </c>
+      <c r="F83">
+        <f t="shared" si="7"/>
+        <v>141984.26502556371</v>
+      </c>
+      <c r="M83">
+        <v>81</v>
+      </c>
+      <c r="N83">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S83">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T83">
+        <f>SUM($S$2:S83)</f>
+        <v>2117.8217821782232</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>82</v>
+      </c>
+      <c r="B84">
+        <v>20</v>
+      </c>
+      <c r="C84">
+        <v>57260.595174070229</v>
+      </c>
+      <c r="D84">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="E84">
+        <f t="shared" si="6"/>
+        <v>2.44</v>
+      </c>
+      <c r="F84">
+        <f t="shared" si="7"/>
+        <v>139715.85222473135</v>
+      </c>
+      <c r="M84">
+        <v>82</v>
+      </c>
+      <c r="N84">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S84">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T84">
+        <f>SUM($S$2:S84)</f>
+        <v>2132.6732673267379</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>83</v>
+      </c>
+      <c r="B85">
+        <v>20</v>
+      </c>
+      <c r="C85">
+        <v>58184.15316074877</v>
+      </c>
+      <c r="D85">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="E85">
+        <f t="shared" si="6"/>
+        <v>2.3600000000000003</v>
+      </c>
+      <c r="F85">
+        <f t="shared" si="7"/>
+        <v>137314.60145936711</v>
+      </c>
+      <c r="M85">
+        <v>83</v>
+      </c>
+      <c r="N85">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S85">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T85">
+        <f>SUM($S$2:S85)</f>
+        <v>2147.5247524752526</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>84</v>
+      </c>
+      <c r="B86">
+        <v>20</v>
+      </c>
+      <c r="C86">
+        <v>59107.711147427333</v>
+      </c>
+      <c r="D86">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="E86">
+        <f t="shared" si="6"/>
+        <v>2.2800000000000002</v>
+      </c>
+      <c r="F86">
+        <f t="shared" si="7"/>
+        <v>134765.58141613434</v>
+      </c>
+      <c r="M86">
+        <v>84</v>
+      </c>
+      <c r="N86">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S86">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T86">
+        <f>SUM($S$2:S86)</f>
+        <v>2162.3762376237673</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>85</v>
+      </c>
+      <c r="B87">
+        <v>20</v>
+      </c>
+      <c r="C87">
+        <v>60031.269134105882</v>
+      </c>
+      <c r="D87">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="E87">
+        <f t="shared" si="6"/>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F87">
+        <f t="shared" si="7"/>
+        <v>132068.79209503296</v>
+      </c>
+      <c r="M87">
+        <v>85</v>
+      </c>
+      <c r="N87">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S87">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T87">
+        <f>SUM($S$2:S87)</f>
+        <v>2177.227722772282</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>86</v>
+      </c>
+      <c r="B88">
+        <v>20</v>
+      </c>
+      <c r="C88">
+        <v>60954.82712078443</v>
+      </c>
+      <c r="D88">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="E88">
+        <f t="shared" si="6"/>
+        <v>2.12</v>
+      </c>
+      <c r="F88">
+        <f t="shared" si="7"/>
+        <v>129224.233496063</v>
+      </c>
+      <c r="M88">
+        <v>86</v>
+      </c>
+      <c r="N88">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S88">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T88">
+        <f>SUM($S$2:S88)</f>
+        <v>2192.0792079207968</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>87</v>
+      </c>
+      <c r="B89">
+        <v>21</v>
+      </c>
+      <c r="C89">
+        <v>61886.211128846291</v>
+      </c>
+      <c r="D89">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="E89">
+        <f t="shared" si="6"/>
+        <v>2.04</v>
+      </c>
+      <c r="F89">
+        <f t="shared" si="7"/>
+        <v>126247.87070284644</v>
+      </c>
+      <c r="M89">
+        <v>87</v>
+      </c>
+      <c r="N89">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S89">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T89">
+        <f>SUM($S$2:S89)</f>
+        <v>2206.9306930693115</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>88</v>
+      </c>
+      <c r="B90">
+        <v>21</v>
+      </c>
+      <c r="C90">
+        <v>62823.880994434883</v>
+      </c>
+      <c r="D90">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="E90">
+        <f t="shared" si="6"/>
+        <v>1.96</v>
+      </c>
+      <c r="F90">
+        <f t="shared" si="7"/>
+        <v>123134.80674909237</v>
+      </c>
+      <c r="M90">
+        <v>88</v>
+      </c>
+      <c r="N90">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S90">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T90">
+        <f>SUM($S$2:S90)</f>
+        <v>2221.7821782178262</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>89</v>
+      </c>
+      <c r="B91">
+        <v>21</v>
+      </c>
+      <c r="C91">
+        <v>63761.550860023468</v>
+      </c>
+      <c r="D91">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="E91">
+        <f t="shared" si="6"/>
+        <v>1.88</v>
+      </c>
+      <c r="F91">
+        <f t="shared" si="7"/>
+        <v>119871.71561684411</v>
+      </c>
+      <c r="M91">
+        <v>89</v>
+      </c>
+      <c r="N91">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S91">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T91">
+        <f>SUM($S$2:S91)</f>
+        <v>2236.6336633663409</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>90</v>
+      </c>
+      <c r="B92">
+        <v>21</v>
+      </c>
+      <c r="C92">
+        <v>64699.220725612031</v>
+      </c>
+      <c r="D92">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="E92">
+        <f t="shared" si="6"/>
+        <v>1.8</v>
+      </c>
+      <c r="F92">
+        <f t="shared" si="7"/>
+        <v>116458.59730610166</v>
+      </c>
+      <c r="M92">
+        <v>90</v>
+      </c>
+      <c r="N92">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S92">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T92">
+        <f>SUM($S$2:S92)</f>
+        <v>2251.4851485148556</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>91</v>
+      </c>
+      <c r="B93">
+        <v>21</v>
+      </c>
+      <c r="C93">
+        <v>65636.890591200616</v>
+      </c>
+      <c r="D93">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="E93">
+        <f t="shared" si="6"/>
+        <v>1.72</v>
+      </c>
+      <c r="F93">
+        <f t="shared" si="7"/>
+        <v>112895.45181686505</v>
+      </c>
+      <c r="M93">
+        <v>91</v>
+      </c>
+      <c r="N93">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S93">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T93">
+        <f>SUM($S$2:S93)</f>
+        <v>2266.3366336633703</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>92</v>
+      </c>
+      <c r="B94">
+        <v>22</v>
+      </c>
+      <c r="C94">
+        <v>66580.803695104405</v>
+      </c>
+      <c r="D94">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="E94">
+        <f t="shared" si="6"/>
+        <v>1.6400000000000001</v>
+      </c>
+      <c r="F94">
+        <f t="shared" si="7"/>
+        <v>109192.51805997123</v>
+      </c>
+      <c r="M94">
+        <v>92</v>
+      </c>
+      <c r="N94">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S94">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T94">
+        <f>SUM($S$2:S94)</f>
+        <v>2281.188118811885</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>93</v>
+      </c>
+      <c r="B95">
+        <v>22</v>
+      </c>
+      <c r="C95">
+        <v>67531.958033605901</v>
+      </c>
+      <c r="D95">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="E95">
+        <f t="shared" si="6"/>
+        <v>1.56</v>
+      </c>
+      <c r="F95">
+        <f t="shared" si="7"/>
+        <v>105349.8545324252</v>
+      </c>
+      <c r="M95">
+        <v>93</v>
+      </c>
+      <c r="N95">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S95">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T95">
+        <f>SUM($S$2:S95)</f>
+        <v>2296.0396039603997</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>94</v>
+      </c>
+      <c r="B96">
+        <v>22</v>
+      </c>
+      <c r="C96">
+        <v>68483.112372107396</v>
+      </c>
+      <c r="D96">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="E96">
+        <f t="shared" si="6"/>
+        <v>1.48</v>
+      </c>
+      <c r="F96">
+        <f t="shared" si="7"/>
+        <v>101355.00631071895</v>
+      </c>
+      <c r="M96">
+        <v>94</v>
+      </c>
+      <c r="N96">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S96">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T96">
+        <f>SUM($S$2:S96)</f>
+        <v>2310.8910891089145</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>95</v>
+      </c>
+      <c r="B97">
+        <v>22</v>
+      </c>
+      <c r="C97">
+        <v>69434.266710608877</v>
+      </c>
+      <c r="D97">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="E97">
+        <f t="shared" si="6"/>
+        <v>1.4</v>
+      </c>
+      <c r="F97">
+        <f t="shared" si="7"/>
+        <v>97207.973394852423</v>
+      </c>
+      <c r="M97">
+        <v>95</v>
+      </c>
+      <c r="N97">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S97">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T97">
+        <f>SUM($S$2:S97)</f>
+        <v>2325.7425742574292</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>96</v>
+      </c>
+      <c r="B98">
+        <v>22</v>
+      </c>
+      <c r="C98">
+        <v>70385.421049110373</v>
+      </c>
+      <c r="D98">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="E98">
+        <f t="shared" si="6"/>
+        <v>1.32</v>
+      </c>
+      <c r="F98">
+        <f t="shared" si="7"/>
+        <v>92908.755784825698</v>
+      </c>
+      <c r="M98">
+        <v>96</v>
+      </c>
+      <c r="N98">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S98">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T98">
+        <f>SUM($S$2:S98)</f>
+        <v>2340.5940594059439</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>97</v>
+      </c>
+      <c r="B99">
+        <v>23</v>
+      </c>
+      <c r="C99">
+        <v>71340.797195344814</v>
+      </c>
+      <c r="D99">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="F77">
+      <c r="E99">
         <f t="shared" si="6"/>
-        <v>152736.78965482398</v>
-      </c>
-      <c r="M77">
-        <v>75</v>
-      </c>
-      <c r="N77">
+        <v>1.24</v>
+      </c>
+      <c r="F99">
         <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A78">
-        <v>76</v>
-      </c>
-      <c r="B78">
-        <v>18</v>
-      </c>
-      <c r="C78">
-        <v>51805.460818595267</v>
-      </c>
-      <c r="D78">
-        <f t="shared" si="4"/>
-        <v>24</v>
-      </c>
-      <c r="E78">
-        <f t="shared" si="5"/>
-        <v>2.92</v>
-      </c>
-      <c r="F78">
-        <f t="shared" si="6"/>
-        <v>151271.94559029819</v>
-      </c>
-      <c r="M78">
-        <v>76</v>
-      </c>
-      <c r="N78">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A79">
-        <v>77</v>
-      </c>
-      <c r="B79">
-        <v>19</v>
-      </c>
-      <c r="C79">
-        <v>52707.932485168298</v>
-      </c>
-      <c r="D79">
-        <f t="shared" si="4"/>
-        <v>23</v>
-      </c>
-      <c r="E79">
-        <f t="shared" si="5"/>
-        <v>2.84</v>
-      </c>
-      <c r="F79">
-        <f t="shared" si="6"/>
-        <v>149690.52825787794</v>
-      </c>
-      <c r="M79">
-        <v>77</v>
-      </c>
-      <c r="N79">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A80">
-        <v>78</v>
-      </c>
-      <c r="B80">
-        <v>19</v>
-      </c>
-      <c r="C80">
-        <v>53616.689941809127</v>
-      </c>
-      <c r="D80">
-        <f t="shared" si="4"/>
-        <v>22</v>
-      </c>
-      <c r="E80">
-        <f t="shared" si="5"/>
-        <v>2.76</v>
-      </c>
-      <c r="F80">
-        <f t="shared" si="6"/>
-        <v>147982.06423939319</v>
-      </c>
-      <c r="M80">
-        <v>78</v>
-      </c>
-      <c r="N80">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A81">
-        <v>79</v>
-      </c>
-      <c r="B81">
-        <v>19</v>
-      </c>
-      <c r="C81">
-        <v>54525.447398449956</v>
-      </c>
-      <c r="D81">
-        <f t="shared" si="4"/>
-        <v>21</v>
-      </c>
-      <c r="E81">
-        <f t="shared" si="5"/>
-        <v>2.6799999999999997</v>
-      </c>
-      <c r="F81">
-        <f t="shared" si="6"/>
-        <v>146128.19902784587</v>
-      </c>
-      <c r="M81">
-        <v>79</v>
-      </c>
-      <c r="N81">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A82">
-        <v>80</v>
-      </c>
-      <c r="B82">
-        <v>19</v>
-      </c>
-      <c r="C82">
-        <v>55434.204855090793</v>
-      </c>
-      <c r="D82">
-        <f t="shared" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="E82">
-        <f t="shared" si="5"/>
-        <v>2.6</v>
-      </c>
-      <c r="F82">
-        <f t="shared" si="6"/>
-        <v>144128.93262323606</v>
-      </c>
-      <c r="M82">
-        <v>80</v>
-      </c>
-      <c r="N82">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A83">
-        <v>81</v>
-      </c>
-      <c r="B83">
-        <v>19</v>
-      </c>
-      <c r="C83">
-        <v>56342.96231173163</v>
-      </c>
-      <c r="D83">
-        <f t="shared" si="4"/>
-        <v>19</v>
-      </c>
-      <c r="E83">
-        <f t="shared" si="5"/>
-        <v>2.52</v>
-      </c>
-      <c r="F83">
-        <f t="shared" si="6"/>
-        <v>141984.26502556371</v>
-      </c>
-      <c r="M83">
-        <v>81</v>
-      </c>
-      <c r="N83">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A84">
-        <v>82</v>
-      </c>
-      <c r="B84">
-        <v>20</v>
-      </c>
-      <c r="C84">
-        <v>57260.595174070229</v>
-      </c>
-      <c r="D84">
-        <f t="shared" si="4"/>
-        <v>18</v>
-      </c>
-      <c r="E84">
-        <f t="shared" si="5"/>
-        <v>2.44</v>
-      </c>
-      <c r="F84">
-        <f t="shared" si="6"/>
-        <v>139715.85222473135</v>
-      </c>
-      <c r="M84">
-        <v>82</v>
-      </c>
-      <c r="N84">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A85">
-        <v>83</v>
-      </c>
-      <c r="B85">
-        <v>20</v>
-      </c>
-      <c r="C85">
-        <v>58184.15316074877</v>
-      </c>
-      <c r="D85">
-        <f t="shared" si="4"/>
-        <v>17</v>
-      </c>
-      <c r="E85">
-        <f t="shared" si="5"/>
-        <v>2.3600000000000003</v>
-      </c>
-      <c r="F85">
-        <f t="shared" si="6"/>
-        <v>137314.60145936711</v>
-      </c>
-      <c r="M85">
-        <v>83</v>
-      </c>
-      <c r="N85">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A86">
-        <v>84</v>
-      </c>
-      <c r="B86">
-        <v>20</v>
-      </c>
-      <c r="C86">
-        <v>59107.711147427333</v>
-      </c>
-      <c r="D86">
-        <f t="shared" si="4"/>
-        <v>16</v>
-      </c>
-      <c r="E86">
-        <f t="shared" si="5"/>
-        <v>2.2800000000000002</v>
-      </c>
-      <c r="F86">
-        <f t="shared" si="6"/>
-        <v>134765.58141613434</v>
-      </c>
-      <c r="M86">
-        <v>84</v>
-      </c>
-      <c r="N86">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A87">
-        <v>85</v>
-      </c>
-      <c r="B87">
-        <v>20</v>
-      </c>
-      <c r="C87">
-        <v>60031.269134105882</v>
-      </c>
-      <c r="D87">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="E87">
-        <f t="shared" si="5"/>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="F87">
-        <f t="shared" si="6"/>
-        <v>132068.79209503296</v>
-      </c>
-      <c r="M87">
-        <v>85</v>
-      </c>
-      <c r="N87">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A88">
-        <v>86</v>
-      </c>
-      <c r="B88">
-        <v>20</v>
-      </c>
-      <c r="C88">
-        <v>60954.82712078443</v>
-      </c>
-      <c r="D88">
-        <f t="shared" si="4"/>
-        <v>14</v>
-      </c>
-      <c r="E88">
-        <f t="shared" si="5"/>
-        <v>2.12</v>
-      </c>
-      <c r="F88">
-        <f t="shared" si="6"/>
-        <v>129224.233496063</v>
-      </c>
-      <c r="M88">
-        <v>86</v>
-      </c>
-      <c r="N88">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A89">
-        <v>87</v>
-      </c>
-      <c r="B89">
-        <v>21</v>
-      </c>
-      <c r="C89">
-        <v>61886.211128846291</v>
-      </c>
-      <c r="D89">
-        <f t="shared" si="4"/>
-        <v>13</v>
-      </c>
-      <c r="E89">
-        <f t="shared" si="5"/>
-        <v>2.04</v>
-      </c>
-      <c r="F89">
-        <f t="shared" si="6"/>
-        <v>126247.87070284644</v>
-      </c>
-      <c r="M89">
-        <v>87</v>
-      </c>
-      <c r="N89">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A90">
-        <v>88</v>
-      </c>
-      <c r="B90">
-        <v>21</v>
-      </c>
-      <c r="C90">
-        <v>62823.880994434883</v>
-      </c>
-      <c r="D90">
-        <f t="shared" si="4"/>
-        <v>12</v>
-      </c>
-      <c r="E90">
-        <f t="shared" si="5"/>
-        <v>1.96</v>
-      </c>
-      <c r="F90">
-        <f t="shared" si="6"/>
-        <v>123134.80674909237</v>
-      </c>
-      <c r="M90">
-        <v>88</v>
-      </c>
-      <c r="N90">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A91">
-        <v>89</v>
-      </c>
-      <c r="B91">
-        <v>21</v>
-      </c>
-      <c r="C91">
-        <v>63761.550860023468</v>
-      </c>
-      <c r="D91">
-        <f t="shared" si="4"/>
-        <v>11</v>
-      </c>
-      <c r="E91">
-        <f t="shared" si="5"/>
-        <v>1.88</v>
-      </c>
-      <c r="F91">
-        <f t="shared" si="6"/>
-        <v>119871.71561684411</v>
-      </c>
-      <c r="M91">
-        <v>89</v>
-      </c>
-      <c r="N91">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A92">
-        <v>90</v>
-      </c>
-      <c r="B92">
-        <v>21</v>
-      </c>
-      <c r="C92">
-        <v>64699.220725612031</v>
-      </c>
-      <c r="D92">
-        <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="E92">
-        <f t="shared" si="5"/>
-        <v>1.8</v>
-      </c>
-      <c r="F92">
-        <f t="shared" si="6"/>
-        <v>116458.59730610166</v>
-      </c>
-      <c r="M92">
-        <v>90</v>
-      </c>
-      <c r="N92">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A93">
-        <v>91</v>
-      </c>
-      <c r="B93">
-        <v>21</v>
-      </c>
-      <c r="C93">
-        <v>65636.890591200616</v>
-      </c>
-      <c r="D93">
-        <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="E93">
-        <f t="shared" si="5"/>
-        <v>1.72</v>
-      </c>
-      <c r="F93">
-        <f t="shared" si="6"/>
-        <v>112895.45181686505</v>
-      </c>
-      <c r="M93">
-        <v>91</v>
-      </c>
-      <c r="N93">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A94">
-        <v>92</v>
-      </c>
-      <c r="B94">
-        <v>22</v>
-      </c>
-      <c r="C94">
-        <v>66580.803695104405</v>
-      </c>
-      <c r="D94">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="E94">
-        <f t="shared" si="5"/>
-        <v>1.6400000000000001</v>
-      </c>
-      <c r="F94">
-        <f t="shared" si="6"/>
-        <v>109192.51805997123</v>
-      </c>
-      <c r="M94">
-        <v>92</v>
-      </c>
-      <c r="N94">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A95">
-        <v>93</v>
-      </c>
-      <c r="B95">
-        <v>22</v>
-      </c>
-      <c r="C95">
-        <v>67531.958033605901</v>
-      </c>
-      <c r="D95">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="E95">
-        <f t="shared" si="5"/>
-        <v>1.56</v>
-      </c>
-      <c r="F95">
-        <f t="shared" si="6"/>
-        <v>105349.8545324252</v>
-      </c>
-      <c r="M95">
-        <v>93</v>
-      </c>
-      <c r="N95">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A96">
-        <v>94</v>
-      </c>
-      <c r="B96">
-        <v>22</v>
-      </c>
-      <c r="C96">
-        <v>68483.112372107396</v>
-      </c>
-      <c r="D96">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="E96">
-        <f t="shared" si="5"/>
-        <v>1.48</v>
-      </c>
-      <c r="F96">
-        <f t="shared" si="6"/>
-        <v>101355.00631071895</v>
-      </c>
-      <c r="M96">
-        <v>94</v>
-      </c>
-      <c r="N96">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A97">
-        <v>95</v>
-      </c>
-      <c r="B97">
-        <v>22</v>
-      </c>
-      <c r="C97">
-        <v>69434.266710608877</v>
-      </c>
-      <c r="D97">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="E97">
-        <f t="shared" si="5"/>
-        <v>1.4</v>
-      </c>
-      <c r="F97">
-        <f t="shared" si="6"/>
-        <v>97207.973394852423</v>
-      </c>
-      <c r="M97">
-        <v>95</v>
-      </c>
-      <c r="N97">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A98">
-        <v>96</v>
-      </c>
-      <c r="B98">
-        <v>22</v>
-      </c>
-      <c r="C98">
-        <v>70385.421049110373</v>
-      </c>
-      <c r="D98">
-        <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="E98">
-        <f t="shared" si="5"/>
-        <v>1.32</v>
-      </c>
-      <c r="F98">
-        <f t="shared" si="6"/>
-        <v>92908.755784825698</v>
-      </c>
-      <c r="M98">
-        <v>96</v>
-      </c>
-      <c r="N98">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A99">
-        <v>97</v>
-      </c>
-      <c r="B99">
-        <v>23</v>
-      </c>
-      <c r="C99">
-        <v>71340.797195344814</v>
-      </c>
-      <c r="D99">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="E99">
-        <f t="shared" si="5"/>
-        <v>1.24</v>
-      </c>
-      <c r="F99">
-        <f t="shared" si="6"/>
         <v>88462.588522227568</v>
       </c>
       <c r="M99">
         <v>97</v>
       </c>
       <c r="N99">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S99">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T99">
+        <f>SUM($S$2:S99)</f>
+        <v>2355.4455445544586</v>
+      </c>
+    </row>
+    <row r="100" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>98</v>
       </c>
@@ -3423,26 +4223,34 @@
         <v>72304.862022308938</v>
       </c>
       <c r="D100">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="E100">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.1599999999999999</v>
       </c>
       <c r="F100">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>83873.639945878356</v>
       </c>
       <c r="M100">
         <v>98</v>
       </c>
       <c r="N100">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S100">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T100">
+        <f>SUM($S$2:S100)</f>
+        <v>2370.2970297029733</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>99</v>
       </c>
@@ -3453,26 +4261,34 @@
         <v>73268.926849273048</v>
       </c>
       <c r="D101">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.08</v>
       </c>
       <c r="F101">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>79130.440997214901</v>
       </c>
       <c r="M101">
         <v>99</v>
       </c>
       <c r="N101">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S101">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T101">
+        <f>SUM($S$2:S101)</f>
+        <v>2385.148514851488</v>
+      </c>
+    </row>
+    <row r="102" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>100</v>
       </c>
@@ -3483,26 +4299,34 @@
         <v>74232.991676237172</v>
       </c>
       <c r="D102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E102">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F102">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>74232.991676237172</v>
       </c>
       <c r="M102">
         <v>100</v>
       </c>
       <c r="N102">
-        <f t="shared" si="7"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
+        <f t="shared" si="8"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="S102">
+        <f t="shared" si="9"/>
+        <v>14.851485148514852</v>
+      </c>
+      <c r="T102">
+        <f>SUM($S$2:S102)</f>
+        <v>2400.0000000000027</v>
+      </c>
+    </row>
+    <row r="103" spans="1:20" x14ac:dyDescent="0.35">
       <c r="E103" t="s">
         <v>6</v>
       </c>
@@ -3514,15 +4338,23 @@
         <v>101</v>
       </c>
       <c r="N103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9.9009900990099011E-3</v>
       </c>
       <c r="P103">
         <f>1/2</f>
         <v>0.5</v>
       </c>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="S103">
+        <f t="shared" si="9"/>
+        <v>64.851485148514854</v>
+      </c>
+      <c r="T103">
+        <f>SUM($S$2:S103)</f>
+        <v>2464.8514851485174</v>
+      </c>
+    </row>
+    <row r="104" spans="1:20" x14ac:dyDescent="0.35">
       <c r="E104" t="s">
         <v>7</v>
       </c>
@@ -3534,13 +4366,34 @@
         <v>102</v>
       </c>
       <c r="N104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9.9009900990099011E-3</v>
       </c>
       <c r="P104">
         <f>1/2</f>
         <v>0.5</v>
       </c>
+      <c r="S104">
+        <f t="shared" si="9"/>
+        <v>64.851485148514854</v>
+      </c>
+      <c r="T104">
+        <f>SUM($S$2:S104)</f>
+        <v>2529.7029702970322</v>
+      </c>
+    </row>
+    <row r="105" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="S105">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="T105">
+        <f>SUM($S$2:S105)</f>
+        <v>2529.7029702970322</v>
+      </c>
+    </row>
+    <row r="106" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="N106" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Manual Trading/Day 2/optimal_allocation.xlsx
+++ b/Manual Trading/Day 2/optimal_allocation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92c4f7ffed9c6980/Python/IntaraTradingAlgorithm/Manual Trading/Day 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="11_3C91D1A4D360D04F55E2DCF0505ED87656CD3EF8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CAD003B-9C92-4598-A270-820A1D908EF8}"/>
+  <xr:revisionPtr revIDLastSave="187" documentId="11_3C91D1A4D360D04F55E2DCF0505ED87656CD3EF8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57673FE8-D3E5-455D-915B-B7607BA1847A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>Allocation</t>
   </si>
@@ -62,25 +62,49 @@
     <t>Estimate 5000 traders submit manual</t>
   </si>
   <si>
-    <t>All 100/99 (put down other teams)</t>
+    <t>Linear</t>
   </si>
   <si>
     <t>Linear (Uninformed)</t>
   </si>
   <si>
-    <t>All 0/1 (ensure success)</t>
-  </si>
-  <si>
     <t>normally distributed around linear maximisation (36)</t>
-  </si>
-  <si>
-    <t>normally distributed + 5 to capture excess scale not being used by others</t>
   </si>
   <si>
     <t>cumulative quantity</t>
   </si>
   <si>
     <t>quantity at this price</t>
+  </si>
+  <si>
+    <t>0/1</t>
+  </si>
+  <si>
+    <t>trader types</t>
+  </si>
+  <si>
+    <t>100/99</t>
+  </si>
+  <si>
+    <t>normal distribution + 2 (beat traders)</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>Strategy performance (weighted)</t>
+  </si>
+  <si>
+    <t>around 5</t>
+  </si>
+  <si>
+    <t>1/0</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">index </t>
   </si>
 </sst>
 </file>
@@ -116,9 +140,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -421,11 +451,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T106"/>
+  <dimension ref="A1:W106"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="52.7265625" customWidth="1"/>
     <col min="6" max="6" width="28.81640625" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" customWidth="1"/>
     <col min="13" max="13" width="33.90625" customWidth="1"/>
     <col min="14" max="14" width="20.08984375" customWidth="1"/>
     <col min="15" max="15" width="29.90625" customWidth="1"/>
@@ -437,7 +468,7 @@
     <col min="21" max="21" width="17.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -463,25 +494,31 @@
         <v>10</v>
       </c>
       <c r="O1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T1" t="s">
         <v>12</v>
       </c>
-      <c r="R1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S1" t="s">
-        <v>15</v>
-      </c>
-      <c r="T1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U1" t="s">
+        <v>18</v>
+      </c>
+      <c r="W1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -503,8 +540,11 @@
         <f>E2*C2</f>
         <v>0</v>
       </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
       <c r="M2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N2">
         <f>1/101</f>
@@ -514,16 +554,28 @@
         <f>0.5</f>
         <v>0.5</v>
       </c>
+      <c r="R2">
+        <f>_xlfn.NORM.DIST(M2,36,10,FALSE)</f>
+        <v>5.0881402816450391E-11</v>
+      </c>
       <c r="S2">
-        <f>(0.3*N2+0.18*O2+0.02*P2+0.3*Q2+0.2*R2)*5000</f>
-        <v>464.85148514851483</v>
+        <f>($J$3*N2+$J$4*O2+$J$5*P2+$J$6*Q2+$J$7*R2)*5000</f>
+        <v>59.900990264374464</v>
       </c>
       <c r="T2">
         <f>SUM($S$2:S2)</f>
-        <v>464.85148514851483</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+        <v>59.900990264374464</v>
+      </c>
+      <c r="U2">
+        <f>(5000-T2)/5000*8+1</f>
+        <v>8.9041584155770011</v>
+      </c>
+      <c r="W2">
+        <f>U2*C2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -545,8 +597,14 @@
         <f t="shared" ref="F3:F66" si="2">E3*C3</f>
         <v>0</v>
       </c>
+      <c r="I3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3">
+        <v>0.2</v>
+      </c>
       <c r="M3">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="N3">
         <f t="shared" ref="N3:N66" si="3">1/101</f>
@@ -555,16 +613,28 @@
       <c r="O3">
         <v>0.5</v>
       </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R66" si="4">_xlfn.NORM.DIST(M3,36,10,FALSE)</f>
+        <v>9.6014333703123347E-11</v>
+      </c>
       <c r="S3">
-        <f t="shared" ref="S3:S66" si="4">(0.3*N3+0.18*O3+0.02*P3+0.3*Q3+0.2*R3)*5000</f>
-        <v>464.85148514851483</v>
+        <f t="shared" ref="S3:S66" si="5">($J$3*N3+$J$4*O3+$J$5*P3+$J$6*Q3+$J$7*R3)*5000</f>
+        <v>59.90099041105649</v>
       </c>
       <c r="T3">
         <f>SUM($S$2:S3)</f>
-        <v>929.70297029702965</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+        <v>119.80198067543095</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U66" si="6">(5000-T3)/5000*8+1</f>
+        <v>8.8083168309193098</v>
+      </c>
+      <c r="W3">
+        <f t="shared" ref="W3:W66" si="7">U3*C3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -586,23 +656,41 @@
         <f t="shared" si="2"/>
         <v>1858.7574203763625</v>
       </c>
+      <c r="I4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4">
+        <v>0.02</v>
+      </c>
       <c r="M4">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="N4">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R4">
+        <f t="shared" si="4"/>
+        <v>1.7937839079640794E-10</v>
+      </c>
       <c r="S4">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.9009906819896703</v>
       </c>
       <c r="T4">
         <f>SUM($S$2:S4)</f>
-        <v>944.55445544554448</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+        <v>129.70297135742064</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="6"/>
+        <v>8.7924752458281272</v>
+      </c>
+      <c r="W4">
+        <f t="shared" si="7"/>
+        <v>1848.7645482645378</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -624,23 +712,41 @@
         <f t="shared" si="2"/>
         <v>3683.8721725106184</v>
       </c>
+      <c r="I5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5">
+        <v>0.08</v>
+      </c>
       <c r="M5">
-        <v>3</v>
+        <v>97</v>
       </c>
       <c r="N5">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R5">
+        <f t="shared" si="4"/>
+        <v>3.3178842435473048E-10</v>
+      </c>
       <c r="S5">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.900991177322279</v>
       </c>
       <c r="T5">
         <f>SUM($S$2:S5)</f>
-        <v>959.4059405940593</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+        <v>139.60396253474292</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="6"/>
+        <v>8.7766336599444124</v>
+      </c>
+      <c r="W5">
+        <f t="shared" si="7"/>
+        <v>3690.867181300142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -662,23 +768,41 @@
         <f t="shared" si="2"/>
         <v>5785.4768832915688</v>
       </c>
+      <c r="I6" s="3">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>0.05</v>
+      </c>
       <c r="M6">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="N6">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R6">
+        <f t="shared" si="4"/>
+        <v>6.0758828498232861E-10</v>
+      </c>
       <c r="S6">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.9009920736718282</v>
       </c>
       <c r="T6">
         <f>SUM($S$2:S6)</f>
-        <v>974.25742574257413</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+        <v>149.50495460841475</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="6"/>
+        <v>8.7607920726265363</v>
+      </c>
+      <c r="W6">
+        <f t="shared" si="7"/>
+        <v>5839.3271907263661</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -700,23 +824,41 @@
         <f t="shared" si="2"/>
         <v>8598.2317735554425</v>
       </c>
+      <c r="I7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7">
+        <v>0.65</v>
+      </c>
       <c r="M7">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="N7">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R7">
+        <f t="shared" si="4"/>
+        <v>1.1015763624682308E-9</v>
+      </c>
       <c r="S7">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.9009936791330784</v>
       </c>
       <c r="T7">
         <f>SUM($S$2:S7)</f>
-        <v>989.10891089108895</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+        <v>159.40594828754783</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="6"/>
+        <v>8.7449504827399238</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="7"/>
+        <v>8743.1524533562097</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -739,22 +881,34 @@
         <v>11357.664296231373</v>
       </c>
       <c r="M8">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="N8">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R8">
+        <f t="shared" si="4"/>
+        <v>1.9773196406244672E-9</v>
+      </c>
       <c r="S8">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.9009965252987335</v>
       </c>
       <c r="T8">
         <f>SUM($S$2:S8)</f>
-        <v>1003.9603960396038</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+        <v>169.30694481284655</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="6"/>
+        <v>8.7291088882994465</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="7"/>
+        <v>11636.418821426591</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -777,22 +931,34 @@
         <v>14197.205998168776</v>
       </c>
       <c r="M9">
-        <v>7</v>
+        <v>93</v>
       </c>
       <c r="N9">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R9">
+        <f t="shared" si="4"/>
+        <v>3.5139550948204335E-9</v>
+      </c>
       <c r="S9">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.9010015193639607</v>
       </c>
       <c r="T9">
         <f>SUM($S$2:S9)</f>
-        <v>1018.8118811881186</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+        <v>179.20794633221053</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="6"/>
+        <v>8.7132672858684632</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="7"/>
+        <v>14656.878030163449</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -815,22 +981,34 @@
         <v>17578.294156500444</v>
       </c>
       <c r="M10">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="N10">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R10">
+        <f t="shared" si="4"/>
+        <v>6.1826205001658568E-9</v>
+      </c>
       <c r="S10">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.9010101925265257</v>
       </c>
       <c r="T10">
         <f>SUM($S$2:S10)</f>
-        <v>1033.6633663366335</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+        <v>189.10895652473704</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="6"/>
+        <v>8.6974256695604204</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="7"/>
+        <v>18287.787897587426</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -853,22 +1031,34 @@
         <v>20892.096978347894</v>
       </c>
       <c r="M11">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="N11">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R11">
+        <f t="shared" si="4"/>
+        <v>1.0769760042543275E-8</v>
+      </c>
       <c r="S11">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.9010251007300383</v>
       </c>
       <c r="T11">
         <f>SUM($S$2:S11)</f>
-        <v>1048.5148514851485</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+        <v>199.00998162546708</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="6"/>
+        <v>8.6815840293992537</v>
+      </c>
+      <c r="W11">
+        <f t="shared" si="7"/>
+        <v>21905.373848778439</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -891,22 +1081,34 @@
         <v>24138.614463711136</v>
       </c>
       <c r="M12">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="N12">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R12">
+        <f t="shared" si="4"/>
+        <v>1.8573618445552898E-8</v>
+      </c>
       <c r="S12">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.9010504632698506</v>
       </c>
       <c r="T12">
         <f>SUM($S$2:S12)</f>
-        <v>1063.3663366336634</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+        <v>208.91103208873693</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="6"/>
+        <v>8.6657423486580214</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="7"/>
+        <v>25509.635804403737</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -929,22 +1131,34 @@
         <v>27750.658049448539</v>
       </c>
       <c r="M13">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="N13">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R13">
+        <f t="shared" si="4"/>
+        <v>3.1713492167159761E-8</v>
+      </c>
       <c r="S13">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.9010931678594432</v>
       </c>
       <c r="T13">
         <f>SUM($S$2:S13)</f>
-        <v>1078.2178217821784</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+        <v>218.81212525659637</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="6"/>
+        <v>8.6499005995894471</v>
+      </c>
+      <c r="W13">
+        <f t="shared" si="7"/>
+        <v>29561.629766123966</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -967,22 +1181,34 @@
         <v>31402.574344485038</v>
       </c>
       <c r="M14">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="N14">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R14">
+        <f t="shared" si="4"/>
+        <v>5.3610353446976141E-8</v>
+      </c>
       <c r="S14">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.9011643326586043</v>
       </c>
       <c r="T14">
         <f>SUM($S$2:S14)</f>
-        <v>1093.0693069306933</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+        <v>228.71328958925497</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="6"/>
+        <v>8.6340587366571917</v>
+      </c>
+      <c r="W14">
+        <f t="shared" si="7"/>
+        <v>33722.844698075627</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1005,22 +1231,34 @@
         <v>34976.374782943232</v>
       </c>
       <c r="M15">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="N15">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R15">
+        <f t="shared" si="4"/>
+        <v>8.9724351623833366E-8</v>
+      </c>
       <c r="S15">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.9012817031526783</v>
       </c>
       <c r="T15">
         <f>SUM($S$2:S15)</f>
-        <v>1107.9207920792082</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+        <v>238.61457129240765</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="6"/>
+        <v>8.618216685932147</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="7"/>
+        <v>37868.590046203237</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1043,22 +1281,34 @@
         <v>38547.252131668269</v>
       </c>
       <c r="M16">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="N16">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R16">
+        <f t="shared" si="4"/>
+        <v>1.4867195147342977E-7</v>
+      </c>
       <c r="S16">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.901473282852189</v>
       </c>
       <c r="T16">
         <f>SUM($S$2:S16)</f>
-        <v>1122.7722772277232</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+        <v>248.51604457525983</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="6"/>
+        <v>8.6023743286795842</v>
+      </c>
+      <c r="W16">
+        <f t="shared" si="7"/>
+        <v>42080.950784086606</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1081,22 +1331,34 @@
         <v>42395.454967147831</v>
       </c>
       <c r="M17">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="N17">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R17">
+        <f t="shared" si="4"/>
+        <v>2.438960745893352E-7</v>
+      </c>
       <c r="S17">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.9017827612523153</v>
       </c>
       <c r="T17">
         <f>SUM($S$2:S17)</f>
-        <v>1137.6237623762381</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+        <v>258.41782733651212</v>
+      </c>
+      <c r="U17">
+        <f t="shared" si="6"/>
+        <v>8.5865314762615803</v>
+      </c>
+      <c r="W17">
+        <f t="shared" si="7"/>
+        <v>46670.501093057079</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1119,22 +1381,34 @@
         <v>46156.69276679735</v>
       </c>
       <c r="M18">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="N18">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R18">
+        <f t="shared" si="4"/>
+        <v>3.9612990910320755E-7</v>
+      </c>
       <c r="S18">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.9022775212144865</v>
       </c>
       <c r="T18">
         <f>SUM($S$2:S18)</f>
-        <v>1152.4752475247531</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+        <v>268.32010485772662</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="6"/>
+        <v>8.5706878322276374</v>
+      </c>
+      <c r="W18">
+        <f t="shared" si="7"/>
+        <v>51242.824491225321</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1157,22 +1431,34 @@
         <v>49830.965530616842</v>
       </c>
       <c r="M19">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="N19">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R19">
+        <f t="shared" si="4"/>
+        <v>6.3698251788670893E-7</v>
+      </c>
       <c r="S19">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.9030602921930324</v>
       </c>
       <c r="T19">
         <f>SUM($S$2:S19)</f>
-        <v>1167.326732673268</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
+        <v>278.22316514991962</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="6"/>
+        <v>8.5548429357601279</v>
+      </c>
+      <c r="W19">
+        <f t="shared" si="7"/>
+        <v>55797.91668216019</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1195,22 +1481,34 @@
         <v>53551.398129115871</v>
       </c>
       <c r="M20">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="N20">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R20">
+        <f t="shared" si="4"/>
+        <v>1.014085206548676E-6</v>
+      </c>
       <c r="S20">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.9042858759311851</v>
       </c>
       <c r="T20">
         <f>SUM($S$2:S20)</f>
-        <v>1182.1782178217829</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
+        <v>288.1274510258508</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="6"/>
+        <v>8.5389960783586396</v>
+      </c>
+      <c r="W20">
+        <f t="shared" si="7"/>
+        <v>60486.134737452725</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1233,22 +1531,34 @@
         <v>57400.10972305145</v>
       </c>
       <c r="M21">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="N21">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R21">
+        <f t="shared" si="4"/>
+        <v>1.5983741106905478E-6</v>
+      </c>
       <c r="S21">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.906184814869647</v>
       </c>
       <c r="T21">
         <f>SUM($S$2:S21)</f>
-        <v>1197.0297029702979</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
+        <v>298.03363584072042</v>
+      </c>
+      <c r="U21">
+        <f t="shared" si="6"/>
+        <v>8.5231461826548482</v>
+      </c>
+      <c r="W21">
+        <f t="shared" si="7"/>
+        <v>65405.016854277455</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1271,22 +1581,34 @@
         <v>61154.374406706396</v>
       </c>
       <c r="M22">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="N22">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R22">
+        <f t="shared" si="4"/>
+        <v>2.4942471290053532E-6</v>
+      </c>
       <c r="S22">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.9090964021791681</v>
       </c>
       <c r="T22">
         <f>SUM($S$2:S22)</f>
-        <v>1211.8811881188128</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
+        <v>307.94273224289958</v>
+      </c>
+      <c r="U22">
+        <f t="shared" si="6"/>
+        <v>8.5072916284113624</v>
+      </c>
+      <c r="W22">
+        <f t="shared" si="7"/>
+        <v>70305.148301473964</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1309,22 +1631,34 @@
         <v>64814.19218008071</v>
       </c>
       <c r="M23">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="N23">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R23">
+        <f t="shared" si="4"/>
+        <v>3.8535196742087128E-6</v>
+      </c>
       <c r="S23">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.9135140379510798</v>
       </c>
       <c r="T23">
         <f>SUM($S$2:S23)</f>
-        <v>1226.7326732673278</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
+        <v>317.85624628085066</v>
+      </c>
+      <c r="U23">
+        <f t="shared" si="6"/>
+        <v>8.4914300059506402</v>
+      </c>
+      <c r="W23">
+        <f t="shared" si="7"/>
+        <v>75186.499493085881</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1347,22 +1681,34 @@
         <v>68504.883207988561</v>
       </c>
       <c r="M24">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="N24">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R24">
+        <f t="shared" si="4"/>
+        <v>5.8943067756539858E-6</v>
+      </c>
       <c r="S24">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.9201465960307775</v>
       </c>
       <c r="T24">
         <f>SUM($S$2:S24)</f>
-        <v>1241.5841584158427</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
+        <v>327.77639287688146</v>
+      </c>
+      <c r="U24">
+        <f t="shared" si="6"/>
+        <v>8.4755577713969892</v>
+      </c>
+      <c r="W24">
+        <f t="shared" si="7"/>
+        <v>80195.731388413056</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1385,22 +1731,34 @@
         <v>72264.451384043903</v>
       </c>
       <c r="M25">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="N25">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R25">
+        <f t="shared" si="4"/>
+        <v>8.9261657177132918E-6</v>
+      </c>
       <c r="S25">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.9300001375924687</v>
       </c>
       <c r="T25">
         <f>SUM($S$2:S25)</f>
-        <v>1256.4356435643576</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
+        <v>337.70639301447392</v>
+      </c>
+      <c r="U25">
+        <f t="shared" si="6"/>
+        <v>8.4596697711768414</v>
+      </c>
+      <c r="W25">
+        <f t="shared" si="7"/>
+        <v>85381.75906484283</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1423,22 +1781,34 @@
         <v>75923.091555372957</v>
       </c>
       <c r="M26">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="N26">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R26">
+        <f t="shared" si="4"/>
+        <v>1.3383022576488536E-5</v>
+      </c>
       <c r="S26">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.9444849223834879</v>
       </c>
       <c r="T26">
         <f>SUM($S$2:S26)</f>
-        <v>1271.2871287128726</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
+        <v>347.6508779368574</v>
+      </c>
+      <c r="U26">
+        <f t="shared" si="6"/>
+        <v>8.443758595301027</v>
+      </c>
+      <c r="W26">
+        <f t="shared" si="7"/>
+        <v>90547.493912783495</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1461,22 +1831,34 @@
         <v>79480.803721975666</v>
       </c>
       <c r="M27">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="N27">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R27">
+        <f t="shared" si="4"/>
+        <v>1.9865547139277272E-5</v>
+      </c>
       <c r="S27">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.9655531272125533</v>
       </c>
       <c r="T27">
         <f>SUM($S$2:S27)</f>
-        <v>1286.1386138613875</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
+        <v>357.61643106406996</v>
+      </c>
+      <c r="U27">
+        <f t="shared" si="6"/>
+        <v>8.4278137102974888</v>
+      </c>
+      <c r="W27">
+        <f t="shared" si="7"/>
+        <v>95692.77247336146</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1499,22 +1881,34 @@
         <v>83022.926334423682</v>
       </c>
       <c r="M28">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="N28">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R28">
+        <f t="shared" si="4"/>
+        <v>2.9194692579146026E-5</v>
+      </c>
       <c r="S28">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>9.995872849892125</v>
       </c>
       <c r="T28">
         <f>SUM($S$2:S28)</f>
-        <v>1300.9900990099025</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
+        <v>367.61230391396208</v>
+      </c>
+      <c r="U28">
+        <f t="shared" si="6"/>
+        <v>8.4118203137376604</v>
+      </c>
+      <c r="W28">
+        <f t="shared" si="7"/>
+        <v>100921.08934188592</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1537,22 +1931,34 @@
         <v>86622.186146609689</v>
       </c>
       <c r="M29">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="N29">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R29">
+        <f t="shared" si="4"/>
+        <v>4.2478027055075142E-5</v>
+      </c>
       <c r="S29">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>10.039043686938896</v>
       </c>
       <c r="T29">
         <f>SUM($S$2:S29)</f>
-        <v>1315.8415841584174</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
+        <v>377.65134760090098</v>
+      </c>
+      <c r="U29">
+        <f t="shared" si="6"/>
+        <v>8.3957578438385578</v>
+      </c>
+      <c r="W29">
+        <f t="shared" si="7"/>
+        <v>106324.40040801784</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1575,22 +1981,34 @@
         <v>90114.801223619812</v>
       </c>
       <c r="M30">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="N30">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R30">
+        <f t="shared" si="4"/>
+        <v>6.1190193011377187E-5</v>
+      </c>
       <c r="S30">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>10.099858226296876</v>
       </c>
       <c r="T30">
         <f>SUM($S$2:S30)</f>
-        <v>1330.6930693069323</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
+        <v>387.75120582719785</v>
+      </c>
+      <c r="U30">
+        <f t="shared" si="6"/>
+        <v>8.379598070676483</v>
+      </c>
+      <c r="W30">
+        <f t="shared" si="7"/>
+        <v>111705.00214095257</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1613,22 +2031,34 @@
         <v>93500.771565454052</v>
       </c>
       <c r="M31">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="N31">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R31">
+        <f t="shared" si="4"/>
+        <v>8.726826950457601E-5</v>
+      </c>
       <c r="S31">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>10.184611974899774</v>
       </c>
       <c r="T31">
         <f>SUM($S$2:S31)</f>
-        <v>1345.5445544554473</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
+        <v>397.93581780209763</v>
+      </c>
+      <c r="U31">
+        <f t="shared" si="6"/>
+        <v>8.363302691516644</v>
+      </c>
+      <c r="W31">
+        <f t="shared" si="7"/>
+        <v>117062.16384614442</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>30</v>
       </c>
@@ -1651,22 +2081,34 @@
         <v>96810.822125695006</v>
       </c>
       <c r="M32">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="N32">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R32">
+        <f t="shared" si="4"/>
+        <v>1.2322191684730198E-4</v>
+      </c>
       <c r="S32">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>10.301461328763633</v>
       </c>
       <c r="T32">
         <f>SUM($S$2:S32)</f>
-        <v>1360.3960396039622</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
+        <v>408.23727913086128</v>
+      </c>
+      <c r="U32">
+        <f t="shared" si="6"/>
+        <v>8.3468203533906209</v>
+      </c>
+      <c r="W32">
+        <f t="shared" si="7"/>
+        <v>122433.71826473183</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>31</v>
       </c>
@@ -1689,22 +2131,34 @@
         <v>100191.51750151294</v>
       </c>
       <c r="M33">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="N33">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R33">
+        <f t="shared" si="4"/>
+        <v>1.722568939053681E-4</v>
+      </c>
       <c r="S33">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>10.460825004202349</v>
       </c>
       <c r="T33">
         <f>SUM($S$2:S33)</f>
-        <v>1375.2475247524771</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.35">
+        <v>418.69810413506366</v>
+      </c>
+      <c r="U33">
+        <f t="shared" si="6"/>
+        <v>8.3300830333838984</v>
+      </c>
+      <c r="W33">
+        <f t="shared" si="7"/>
+        <v>128006.69632336484</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>32</v>
       </c>
@@ -1727,22 +2181,34 @@
         <v>103460.45435251042</v>
       </c>
       <c r="M34">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="N34">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R34">
+        <f t="shared" si="4"/>
+        <v>2.3840882014648405E-4</v>
+      </c>
       <c r="S34">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>10.675818764485975</v>
       </c>
       <c r="T34">
         <f>SUM($S$2:S34)</f>
-        <v>1390.0990099009921</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.35">
+        <v>429.37392289954965</v>
+      </c>
+      <c r="U34">
+        <f t="shared" si="6"/>
+        <v>8.3130017233607205</v>
+      </c>
+      <c r="W34">
+        <f t="shared" si="7"/>
+        <v>133550.76635591651</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>33</v>
       </c>
@@ -1765,22 +2231,34 @@
         <v>106617.6326786875</v>
       </c>
       <c r="M35">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="N35">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R35">
+        <f t="shared" si="4"/>
+        <v>3.2668190561999186E-4</v>
+      </c>
       <c r="S35">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>10.962706292274875</v>
       </c>
       <c r="T35">
         <f>SUM($S$2:S35)</f>
-        <v>1404.950495049507</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.35">
+        <v>440.33662919182456</v>
+      </c>
+      <c r="U35">
+        <f t="shared" si="6"/>
+        <v>8.2954613932930812</v>
+      </c>
+      <c r="W35">
+        <f t="shared" si="7"/>
+        <v>139063.27920288598</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>34</v>
       </c>
@@ -1803,22 +2281,34 @@
         <v>109663.05248004412</v>
       </c>
       <c r="M36">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="N36">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R36">
+        <f t="shared" si="4"/>
+        <v>4.4318484119380076E-4</v>
+      </c>
       <c r="S36">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>11.341340832889752</v>
       </c>
       <c r="T36">
         <f>SUM($S$2:S36)</f>
-        <v>1419.801980198022</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.35">
+        <v>451.67797002471428</v>
+      </c>
+      <c r="U36">
+        <f t="shared" si="6"/>
+        <v>8.2773152479604573</v>
+      </c>
+      <c r="W36">
+        <f t="shared" si="7"/>
+        <v>144540.70962276385</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1841,22 +2331,34 @@
         <v>112747.49430668967</v>
       </c>
       <c r="M37">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="N37">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R37">
+        <f t="shared" si="4"/>
+        <v>5.9525324197758534E-4</v>
+      </c>
       <c r="S37">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>11.835563135437054</v>
       </c>
       <c r="T37">
         <f>SUM($S$2:S37)</f>
-        <v>1434.6534653465369</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
+        <v>463.51353316015133</v>
+      </c>
+      <c r="U37">
+        <f t="shared" si="6"/>
+        <v>8.2583783469437577</v>
+      </c>
+      <c r="W37">
+        <f t="shared" si="7"/>
+        <v>150179.26865395653</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1879,22 +2381,34 @@
         <v>115744.39544568039</v>
       </c>
       <c r="M38">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="N38">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R38">
+        <f t="shared" si="4"/>
+        <v>7.9154515829799694E-4</v>
+      </c>
       <c r="S38">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>12.473511863478391</v>
       </c>
       <c r="T38">
         <f>SUM($S$2:S38)</f>
-        <v>1449.5049504950518</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
+        <v>475.98704502362972</v>
+      </c>
+      <c r="U38">
+        <f t="shared" si="6"/>
+        <v>8.2384207279621933</v>
+      </c>
+      <c r="W38">
+        <f t="shared" si="7"/>
+        <v>155808.99127208273</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>37</v>
       </c>
@@ -1917,22 +2431,34 @@
         <v>118624.91207441901</v>
       </c>
       <c r="M39">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="N39">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R39">
+        <f t="shared" si="4"/>
+        <v>1.0420934814422591E-3</v>
+      </c>
       <c r="S39">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>13.287793913697243</v>
       </c>
       <c r="T39">
         <f>SUM($S$2:S39)</f>
-        <v>1464.3564356435668</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
+        <v>489.27483893732699</v>
+      </c>
+      <c r="U39">
+        <f t="shared" si="6"/>
+        <v>8.2171602577002751</v>
+      </c>
+      <c r="W39">
+        <f t="shared" si="7"/>
+        <v>161384.09156806383</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1955,22 +2481,34 @@
         <v>121389.04419290561</v>
       </c>
       <c r="M40">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="N40">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R40">
+        <f t="shared" si="4"/>
+        <v>1.3582969233685612E-3</v>
+      </c>
       <c r="S40">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>14.315455099957726</v>
       </c>
       <c r="T40">
         <f>SUM($S$2:S40)</f>
-        <v>1479.2079207920817</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.35">
+        <v>503.59029403728471</v>
+      </c>
+      <c r="U40">
+        <f t="shared" si="6"/>
+        <v>8.1942555295403459</v>
+      </c>
+      <c r="W40">
+        <f t="shared" si="7"/>
+        <v>166894.77292002251</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>39</v>
       </c>
@@ -1993,22 +2531,34 @@
         <v>124105.32749024534</v>
       </c>
       <c r="M41">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="N41">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R41">
+        <f t="shared" si="4"/>
+        <v>1.752830049356854E-3</v>
+      </c>
       <c r="S41">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>15.597687759419678</v>
       </c>
       <c r="T41">
         <f>SUM($S$2:S41)</f>
-        <v>1494.0594059405967</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.35">
+        <v>519.18798179670443</v>
+      </c>
+      <c r="U41">
+        <f t="shared" si="6"/>
+        <v>8.1692992291252722</v>
+      </c>
+      <c r="W41">
+        <f t="shared" si="7"/>
+        <v>172424.07418306134</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>40</v>
       </c>
@@ -2031,22 +2581,34 @@
         <v>126788.84890585078</v>
       </c>
       <c r="M42">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="N42">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R42">
+        <f t="shared" si="4"/>
+        <v>2.2394530294842902E-3</v>
+      </c>
       <c r="S42">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>17.179212444833844</v>
       </c>
       <c r="T42">
         <f>SUM($S$2:S42)</f>
-        <v>1508.9108910891116</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
+        <v>536.3671942415383</v>
+      </c>
+      <c r="U42">
+        <f t="shared" si="6"/>
+        <v>8.1418124892135388</v>
+      </c>
+      <c r="W42">
+        <f t="shared" si="7"/>
+        <v>177981.2126749421</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>41</v>
       </c>
@@ -2069,22 +2631,34 @@
         <v>129351.76261738398</v>
       </c>
       <c r="M43">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="N43">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R43">
+        <f t="shared" si="4"/>
+        <v>2.8327037741601186E-3</v>
+      </c>
       <c r="S43">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>19.107277365030289</v>
       </c>
       <c r="T43">
         <f>SUM($S$2:S43)</f>
-        <v>1523.7623762376265</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
+        <v>555.47447160656861</v>
+      </c>
+      <c r="U43">
+        <f t="shared" si="6"/>
+        <v>8.1112408454294886</v>
+      </c>
+      <c r="W43">
+        <f t="shared" si="7"/>
+        <v>183427.15041440984</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>42</v>
       </c>
@@ -2107,22 +2681,34 @@
         <v>131794.06862484509</v>
       </c>
       <c r="M44">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="N44">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R44">
+        <f t="shared" si="4"/>
+        <v>3.5474592846231421E-3</v>
+      </c>
       <c r="S44">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>21.430232774035115</v>
       </c>
       <c r="T44">
         <f>SUM($S$2:S44)</f>
-        <v>1538.6138613861415</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
+        <v>576.90470438060368</v>
+      </c>
+      <c r="U44">
+        <f t="shared" si="6"/>
+        <v>8.0769524729910334</v>
+      </c>
+      <c r="W44">
+        <f t="shared" si="7"/>
+        <v>188740.14689804835</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>43</v>
       </c>
@@ -2145,22 +2731,34 @@
         <v>134115.76692823405</v>
       </c>
       <c r="M45">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="N45">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R45">
+        <f t="shared" si="4"/>
+        <v>4.3983595980427196E-3</v>
+      </c>
       <c r="S45">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>24.195658792648739</v>
       </c>
       <c r="T45">
         <f>SUM($S$2:S45)</f>
-        <v>1553.4653465346564</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.35">
+        <v>601.10036317325239</v>
+      </c>
+      <c r="U45">
+        <f t="shared" si="6"/>
+        <v>8.0382394189227959</v>
+      </c>
+      <c r="W45">
+        <f t="shared" si="7"/>
+        <v>193894.72021971096</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>44</v>
       </c>
@@ -2183,22 +2781,34 @@
         <v>136443.96170291741</v>
       </c>
       <c r="M46">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="N46">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R46">
+        <f t="shared" si="4"/>
+        <v>5.3990966513188061E-3</v>
+      </c>
       <c r="S46">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>27.448054215796024</v>
       </c>
       <c r="T46">
         <f>SUM($S$2:S46)</f>
-        <v>1568.3168316831714</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.35">
+        <v>628.54841738904838</v>
+      </c>
+      <c r="U46">
+        <f t="shared" si="6"/>
+        <v>7.9943225321775229</v>
+      </c>
+      <c r="W46">
+        <f t="shared" si="7"/>
+        <v>199046.90463890505</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>45</v>
       </c>
@@ -2221,22 +2831,34 @@
         <v>138653.70652064256</v>
       </c>
       <c r="M47">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="N47">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R47">
+        <f t="shared" si="4"/>
+        <v>6.5615814774676604E-3</v>
+      </c>
       <c r="S47">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>31.226129900779799</v>
       </c>
       <c r="T47">
         <f>SUM($S$2:S47)</f>
-        <v>1583.1683168316863</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
+        <v>659.77454728982821</v>
+      </c>
+      <c r="U47">
+        <f t="shared" si="6"/>
+        <v>7.9443607243362759</v>
+      </c>
+      <c r="W47">
+        <f t="shared" si="7"/>
+        <v>203984.27043819285</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>46</v>
       </c>
@@ -2259,22 +2881,34 @@
         <v>140738.95867258043</v>
       </c>
       <c r="M48">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="N48">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R48">
+        <f t="shared" si="4"/>
+        <v>7.8950158300894139E-3</v>
+      </c>
       <c r="S48">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>35.559791546800497</v>
       </c>
       <c r="T48">
         <f>SUM($S$2:S48)</f>
-        <v>1598.0198019802012</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.35">
+        <v>695.33433883662872</v>
+      </c>
+      <c r="U48">
+        <f t="shared" si="6"/>
+        <v>7.8874650578613945</v>
+      </c>
+      <c r="W48">
+        <f t="shared" si="7"/>
+        <v>208660.4546634919</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>47</v>
       </c>
@@ -2297,22 +2931,34 @@
         <v>142699.71815873092</v>
       </c>
       <c r="M49">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="N49">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R49">
+        <f t="shared" si="4"/>
+        <v>9.4049077376886937E-3</v>
+      </c>
       <c r="S49">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>40.466940246498154</v>
       </c>
       <c r="T49">
         <f>SUM($S$2:S49)</f>
-        <v>1612.8712871287162</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.35">
+        <v>735.80127908312693</v>
+      </c>
+      <c r="U49">
+        <f t="shared" si="6"/>
+        <v>7.8227179534669968</v>
+      </c>
+      <c r="W49">
+        <f t="shared" si="7"/>
+        <v>213034.28381583677</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>48</v>
       </c>
@@ -2335,22 +2981,34 @@
         <v>144581.11175753575</v>
       </c>
       <c r="M50">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="N50">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R50">
+        <f t="shared" si="4"/>
+        <v>1.1092083467945555E-2</v>
+      </c>
       <c r="S50">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>45.950261369832958</v>
       </c>
       <c r="T50">
         <f>SUM($S$2:S50)</f>
-        <v>1627.7227722772311</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.35">
+        <v>781.75154045295994</v>
+      </c>
+      <c r="U50">
+        <f t="shared" si="6"/>
+        <v>7.7491975352752638</v>
+      </c>
+      <c r="W50">
+        <f t="shared" si="7"/>
+        <v>217129.37885249098</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>49</v>
       </c>
@@ -2373,22 +3031,34 @@
         <v>146406.38825148466</v>
       </c>
       <c r="M51">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N51">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R51">
+        <f t="shared" si="4"/>
+        <v>1.2951759566589173E-2</v>
+      </c>
       <c r="S51">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>51.994208690424713</v>
       </c>
       <c r="T51">
         <f>SUM($S$2:S51)</f>
-        <v>1642.5742574257461</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.35">
+        <v>833.74574914338461</v>
+      </c>
+      <c r="U51">
+        <f t="shared" si="6"/>
+        <v>7.6660068013705853</v>
+      </c>
+      <c r="W51">
+        <f t="shared" si="7"/>
+        <v>220935.50553149288</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>50</v>
       </c>
@@ -2417,16 +3087,28 @@
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R52">
+        <f t="shared" si="4"/>
+        <v>1.4972746563574486E-2</v>
+      </c>
       <c r="S52">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>58.562416430626982</v>
       </c>
       <c r="T52">
         <f>SUM($S$2:S52)</f>
-        <v>1657.425742574261</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.35">
+        <v>892.30816557401158</v>
+      </c>
+      <c r="U52">
+        <f t="shared" si="6"/>
+        <v>7.5723069350815813</v>
+      </c>
+      <c r="W52">
+        <f t="shared" si="7"/>
+        <v>224297.14586935507</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>51</v>
       </c>
@@ -2449,22 +3131,34 @@
         <v>149672.67250381436</v>
       </c>
       <c r="M53">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N53">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R53">
+        <f t="shared" si="4"/>
+        <v>1.7136859204780735E-2</v>
+      </c>
       <c r="S53">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>65.595782514547295</v>
       </c>
       <c r="T53">
         <f>SUM($S$2:S53)</f>
-        <v>1672.2772277227759</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.35">
+        <v>957.90394808855888</v>
+      </c>
+      <c r="U53">
+        <f t="shared" si="6"/>
+        <v>7.467353683058306</v>
+      </c>
+      <c r="W53">
+        <f t="shared" si="7"/>
+        <v>227166.41916149142</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>52</v>
       </c>
@@ -2487,22 +3181,34 @@
         <v>151113.68026219515</v>
       </c>
       <c r="M54">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="N54">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R54">
+        <f t="shared" si="4"/>
+        <v>1.9418605498321296E-2</v>
+      </c>
       <c r="S54">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>73.011457968554112</v>
       </c>
       <c r="T54">
         <f>SUM($S$2:S54)</f>
-        <v>1687.1287128712909</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1030.9154060571129</v>
+      </c>
+      <c r="U54">
+        <f t="shared" si="6"/>
+        <v>7.3505353503086193</v>
+      </c>
+      <c r="W54">
+        <f t="shared" si="7"/>
+        <v>229497.20014101223</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>53</v>
       </c>
@@ -2525,22 +3231,34 @@
         <v>152501.19958890518</v>
       </c>
       <c r="M55">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="N55">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R55">
+        <f t="shared" si="4"/>
+        <v>2.1785217703255054E-2</v>
+      </c>
       <c r="S55">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>80.70294763458881</v>
       </c>
       <c r="T55">
         <f>SUM($S$2:S55)</f>
-        <v>1701.9801980198058</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1111.6183536917017</v>
+      </c>
+      <c r="U55">
+        <f t="shared" si="6"/>
+        <v>7.221410634093278</v>
+      </c>
+      <c r="W55">
+        <f t="shared" si="7"/>
+        <v>231360.03874439103</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>54</v>
       </c>
@@ -2563,22 +3281,34 @@
         <v>153782.72227452623</v>
       </c>
       <c r="M56">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="N56">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R56">
+        <f t="shared" si="4"/>
+        <v>2.4197072451914336E-2</v>
+      </c>
       <c r="S56">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>88.541475567731482</v>
       </c>
       <c r="T56">
         <f>SUM($S$2:S56)</f>
-        <v>1716.8316831683208</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1200.1598292594331</v>
+      </c>
+      <c r="U56">
+        <f t="shared" si="6"/>
+        <v>7.0797442731849074</v>
+      </c>
+      <c r="W56">
+        <f t="shared" si="7"/>
+        <v>232637.2537046714</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>55</v>
       </c>
@@ -2601,22 +3331,34 @@
         <v>154932.80673598096</v>
       </c>
       <c r="M57">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="N57">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R57">
+        <f t="shared" si="4"/>
+        <v>2.6608524989875482E-2</v>
+      </c>
       <c r="S57">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>96.378696316105206</v>
       </c>
       <c r="T57">
         <f>SUM($S$2:S57)</f>
-        <v>1731.6831683168357</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1296.5385255755382</v>
+      </c>
+      <c r="U57">
+        <f t="shared" si="6"/>
+        <v>6.9255383590791393</v>
+      </c>
+      <c r="W57">
+        <f t="shared" si="7"/>
+        <v>233259.36872387634</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>56</v>
       </c>
@@ -2639,22 +3381,34 @@
         <v>155951.45297326951</v>
       </c>
       <c r="M58">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="N58">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R58">
+        <f t="shared" si="4"/>
+        <v>2.8969155276148274E-2</v>
+      </c>
       <c r="S58">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>104.05074474649177</v>
       </c>
       <c r="T58">
         <f>SUM($S$2:S58)</f>
-        <v>1746.5346534653506</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1400.58927032203</v>
+      </c>
+      <c r="U58">
+        <f t="shared" si="6"/>
+        <v>6.7590571674847526</v>
+      </c>
+      <c r="W58">
+        <f t="shared" si="7"/>
+        <v>233204.59867226522</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>57</v>
       </c>
@@ -2677,22 +3431,34 @@
         <v>156842.11934469864</v>
       </c>
       <c r="M59">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="N59">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R59">
+        <f t="shared" si="4"/>
+        <v>3.1225393336676129E-2</v>
+      </c>
       <c r="S59">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>111.38351844320732</v>
       </c>
       <c r="T59">
         <f>SUM($S$2:S59)</f>
-        <v>1761.3861386138656</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1511.9727887652373</v>
+      </c>
+      <c r="U59">
+        <f t="shared" si="6"/>
+        <v>6.5808435379756203</v>
+      </c>
+      <c r="W59">
+        <f t="shared" si="7"/>
+        <v>232466.99269638766</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>58</v>
       </c>
@@ -2715,22 +3481,34 @@
         <v>157683.1860507513</v>
       </c>
       <c r="M60">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="N60">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R60">
+        <f t="shared" si="4"/>
+        <v>3.3322460289179963E-2</v>
+      </c>
       <c r="S60">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>118.19898603884479</v>
       </c>
       <c r="T60">
         <f>SUM($S$2:S60)</f>
-        <v>1776.2376237623805</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1630.1717748040821</v>
+      </c>
+      <c r="U60">
+        <f t="shared" si="6"/>
+        <v>6.3917251603134693</v>
+      </c>
+      <c r="W60">
+        <f t="shared" si="7"/>
+        <v>231162.29074288468</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>59</v>
       </c>
@@ -2753,22 +3531,34 @@
         <v>158389.68208383553</v>
       </c>
       <c r="M61">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="N61">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R61">
+        <f t="shared" si="4"/>
+        <v>3.5206532676429952E-2</v>
+      </c>
       <c r="S61">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>124.32222129740725</v>
       </c>
       <c r="T61">
         <f>SUM($S$2:S61)</f>
-        <v>1791.0891089108954</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1754.4939961014893</v>
+      </c>
+      <c r="U61">
+        <f t="shared" si="6"/>
+        <v>6.192809606237617</v>
+      </c>
+      <c r="W61">
+        <f t="shared" si="7"/>
+        <v>229176.90297609786</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>60</v>
       </c>
@@ -2791,22 +3581,34 @@
         <v>158961.60744395136</v>
       </c>
       <c r="M62">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="N62">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R62">
+        <f t="shared" si="4"/>
+        <v>3.6827014030332332E-2</v>
+      </c>
       <c r="S62">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>129.58878569758997</v>
       </c>
       <c r="T62">
         <f>SUM($S$2:S62)</f>
-        <v>1805.9405940594104</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1884.0827817990794</v>
+      </c>
+      <c r="U62">
+        <f t="shared" si="6"/>
+        <v>5.9854675491214726</v>
+      </c>
+      <c r="W62">
+        <f t="shared" si="7"/>
+        <v>226537.98640760884</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>61</v>
       </c>
@@ -2829,22 +3631,34 @@
         <v>159398.96213109873</v>
       </c>
       <c r="M63">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="N63">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R63">
+        <f t="shared" si="4"/>
+        <v>3.8138781546052408E-2</v>
+      </c>
       <c r="S63">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>133.85203012368021</v>
       </c>
       <c r="T63">
         <f>SUM($S$2:S63)</f>
-        <v>1820.7920792079253</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.35">
+        <v>2017.9348119227595</v>
+      </c>
+      <c r="U63">
+        <f t="shared" si="6"/>
+        <v>5.7713043009235845</v>
+      </c>
+      <c r="W63">
+        <f t="shared" si="7"/>
+        <v>223286.3873082441</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>62</v>
       </c>
@@ -2867,22 +3681,34 @@
         <v>159721.53106582124</v>
       </c>
       <c r="M64">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="N64">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R64">
+        <f t="shared" si="4"/>
+        <v>3.9104269397545591E-2</v>
+      </c>
       <c r="S64">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>136.98986564103308</v>
       </c>
       <c r="T64">
         <f>SUM($S$2:S64)</f>
-        <v>1835.6435643564403</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.35">
+        <v>2154.9246775637926</v>
+      </c>
+      <c r="U64">
+        <f t="shared" si="6"/>
+        <v>5.5521205158979319</v>
+      </c>
+      <c r="W64">
+        <f t="shared" si="7"/>
+        <v>219503.26471811259</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>63</v>
       </c>
@@ -2905,22 +3731,34 @@
         <v>159962.17908938145</v>
       </c>
       <c r="M65">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="N65">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R65">
+        <f t="shared" si="4"/>
+        <v>3.9695254747701178E-2</v>
+      </c>
       <c r="S65">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>138.91056802903873</v>
       </c>
       <c r="T65">
         <f>SUM($S$2:S65)</f>
-        <v>1850.4950495049552</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.35">
+        <v>2293.8352455928311</v>
+      </c>
+      <c r="U65">
+        <f t="shared" si="6"/>
+        <v>5.32986360705147</v>
+      </c>
+      <c r="W65">
+        <f t="shared" si="7"/>
+        <v>215297.12041241006</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>64</v>
       </c>
@@ -2943,22 +3781,34 @@
         <v>160065.31395662154</v>
       </c>
       <c r="M66">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="N66">
         <f t="shared" si="3"/>
         <v>9.9009900990099011E-3</v>
       </c>
+      <c r="R66">
+        <f t="shared" si="4"/>
+        <v>3.9894228040143274E-2</v>
+      </c>
       <c r="S66">
-        <f t="shared" si="4"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="5"/>
+        <v>139.55723122947555</v>
       </c>
       <c r="T66">
         <f>SUM($S$2:S66)</f>
-        <v>1865.3465346534701</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.35">
+        <v>2433.3924768223069</v>
+      </c>
+      <c r="U66">
+        <f t="shared" si="6"/>
+        <v>5.1065720370843088</v>
+      </c>
+      <c r="W66">
+        <f t="shared" si="7"/>
+        <v>210666.25163866093</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>65</v>
       </c>
@@ -2969,34 +3819,46 @@
         <v>42113.404123037239</v>
       </c>
       <c r="D67">
-        <f t="shared" ref="D67:D102" si="5">100-A67</f>
+        <f t="shared" ref="D67:D102" si="8">100-A67</f>
         <v>35</v>
       </c>
       <c r="E67">
-        <f t="shared" ref="E67:E102" si="6">D67*0.08+1</f>
+        <f t="shared" ref="E67:E102" si="9">D67*0.08+1</f>
         <v>3.8000000000000003</v>
       </c>
       <c r="F67">
-        <f t="shared" ref="F67:F103" si="7">E67*C67</f>
+        <f t="shared" ref="F67:F103" si="10">E67*C67</f>
         <v>160030.93566754152</v>
       </c>
       <c r="M67">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="N67">
-        <f t="shared" ref="N67:N104" si="8">1/101</f>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" ref="N67:N104" si="11">1/101</f>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R67">
+        <f t="shared" ref="R67:R103" si="12">_xlfn.NORM.DIST(M67,36,10,FALSE)</f>
+        <v>3.9695254747701178E-2</v>
       </c>
       <c r="S67">
-        <f t="shared" ref="S67:S105" si="9">(0.3*N67+0.18*O67+0.02*P67+0.3*Q67+0.2*R67)*5000</f>
-        <v>14.851485148514852</v>
+        <f t="shared" ref="S67:S104" si="13">($J$3*N67+$J$4*O67+$J$5*P67+$J$6*Q67+$J$7*R67)*5000</f>
+        <v>138.91056802903873</v>
       </c>
       <c r="T67">
         <f>SUM($S$2:S67)</f>
-        <v>1880.1980198019851</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.35">
+        <v>2572.3030448513455</v>
+      </c>
+      <c r="U67">
+        <f t="shared" ref="U67:U102" si="14">(5000-T67)/5000*8+1</f>
+        <v>4.8843151282378479</v>
+      </c>
+      <c r="W67">
+        <f t="shared" ref="W67:W104" si="15">U67*C67</f>
+        <v>205695.13685974493</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>66</v>
       </c>
@@ -3007,34 +3869,46 @@
         <v>42972.861350038002</v>
       </c>
       <c r="D68">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>34</v>
       </c>
       <c r="E68">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>3.72</v>
       </c>
       <c r="F68">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>159859.04422214138</v>
       </c>
       <c r="M68">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="N68">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R68">
+        <f t="shared" si="12"/>
+        <v>3.9104269397545591E-2</v>
       </c>
       <c r="S68">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>136.98986564103308</v>
       </c>
       <c r="T68">
         <f>SUM($S$2:S68)</f>
-        <v>1895.0495049505</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.35">
+        <v>2709.2929104923787</v>
+      </c>
+      <c r="U68">
+        <f t="shared" si="14"/>
+        <v>4.6651313432121935</v>
+      </c>
+      <c r="W68">
+        <f t="shared" si="15"/>
+        <v>200474.04239157413</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>67</v>
       </c>
@@ -3045,34 +3919,46 @@
         <v>43839.813568121113</v>
       </c>
       <c r="D69">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>33</v>
       </c>
       <c r="E69">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>3.64</v>
       </c>
       <c r="F69">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>159576.92138796087</v>
       </c>
       <c r="M69">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="N69">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R69">
+        <f t="shared" si="12"/>
+        <v>3.8138781546052408E-2</v>
       </c>
       <c r="S69">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>133.85203012368021</v>
       </c>
       <c r="T69">
         <f>SUM($S$2:S69)</f>
-        <v>1909.900990099015</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.35">
+        <v>2843.1449406160591</v>
+      </c>
+      <c r="U69">
+        <f t="shared" si="14"/>
+        <v>4.4509680950143053</v>
+      </c>
+      <c r="W69">
+        <f t="shared" si="15"/>
+        <v>195129.61148308232</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>68</v>
       </c>
@@ -3083,34 +3969,46 @@
         <v>44716.609839483528</v>
       </c>
       <c r="D70">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>32</v>
       </c>
       <c r="E70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>3.56</v>
       </c>
       <c r="F70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>159191.13102856136</v>
       </c>
       <c r="M70">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="N70">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R70">
+        <f t="shared" si="12"/>
+        <v>3.6827014030332332E-2</v>
       </c>
       <c r="S70">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>129.58878569758997</v>
       </c>
       <c r="T70">
         <f>SUM($S$2:S70)</f>
-        <v>1924.7524752475299</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.35">
+        <v>2972.7337263136492</v>
+      </c>
+      <c r="U70">
+        <f t="shared" si="14"/>
+        <v>4.2436260378981618</v>
+      </c>
+      <c r="W70">
+        <f t="shared" si="15"/>
+        <v>189760.56984136545</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>69</v>
       </c>
@@ -3121,34 +4019,46 @@
         <v>45593.406110845957</v>
       </c>
       <c r="D71">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
       <c r="E71">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>3.48</v>
       </c>
       <c r="F71">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>158665.05326574392</v>
       </c>
       <c r="M71">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="N71">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R71">
+        <f t="shared" si="12"/>
+        <v>3.5206532676429952E-2</v>
       </c>
       <c r="S71">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>124.32222129740725</v>
       </c>
       <c r="T71">
         <f>SUM($S$2:S71)</f>
-        <v>1939.6039603960448</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.35">
+        <v>3097.0559476110566</v>
+      </c>
+      <c r="U71">
+        <f t="shared" si="14"/>
+        <v>4.0447104838223096</v>
+      </c>
+      <c r="W71">
+        <f t="shared" si="15"/>
+        <v>184412.1276897068</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>70</v>
       </c>
@@ -3159,34 +4069,46 @@
         <v>46470.202382208372</v>
       </c>
       <c r="D72">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>30</v>
       </c>
       <c r="E72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>3.4</v>
       </c>
       <c r="F72">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>157998.68809950846</v>
       </c>
       <c r="M72">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="N72">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R72">
+        <f t="shared" si="12"/>
+        <v>3.3322460289179963E-2</v>
       </c>
       <c r="S72">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>118.19898603884479</v>
       </c>
       <c r="T72">
         <f>SUM($S$2:S72)</f>
-        <v>1954.4554455445598</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.35">
+        <v>3215.2549336499014</v>
+      </c>
+      <c r="U72">
+        <f t="shared" si="14"/>
+        <v>3.8555921061601577</v>
+      </c>
+      <c r="W72">
+        <f t="shared" si="15"/>
+        <v>179170.14547650755</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>71</v>
       </c>
@@ -3197,34 +4119,46 @@
         <v>47346.998653570801</v>
       </c>
       <c r="D73">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>29</v>
       </c>
       <c r="E73">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>3.32</v>
       </c>
       <c r="F73">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>157192.03552985506</v>
       </c>
       <c r="M73">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="N73">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R73">
+        <f t="shared" si="12"/>
+        <v>3.1225393336676129E-2</v>
       </c>
       <c r="S73">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>111.38351844320732</v>
       </c>
       <c r="T73">
         <f>SUM($S$2:S73)</f>
-        <v>1969.3069306930747</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.35">
+        <v>3326.6384520931088</v>
+      </c>
+      <c r="U73">
+        <f t="shared" si="14"/>
+        <v>3.6773784766510258</v>
+      </c>
+      <c r="W73">
+        <f t="shared" si="15"/>
+        <v>174112.83378266636</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>72</v>
       </c>
@@ -3235,34 +4169,46 @@
         <v>48232.670417312831</v>
       </c>
       <c r="D74">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>28</v>
       </c>
       <c r="E74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>3.24</v>
       </c>
       <c r="F74">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>156273.85215209358</v>
       </c>
       <c r="M74">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="N74">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R74">
+        <f t="shared" si="12"/>
+        <v>2.8969155276148274E-2</v>
       </c>
       <c r="S74">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>104.05074474649177</v>
       </c>
       <c r="T74">
         <f>SUM($S$2:S74)</f>
-        <v>1984.1584158415897</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.35">
+        <v>3430.6891968396003</v>
+      </c>
+      <c r="U74">
+        <f t="shared" si="14"/>
+        <v>3.5108972850566396</v>
+      </c>
+      <c r="W74">
+        <f t="shared" si="15"/>
+        <v>169339.95161917532</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>73</v>
       </c>
@@ -3273,34 +4219,46 @@
         <v>49125.868017633453</v>
       </c>
       <c r="D75">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>27</v>
       </c>
       <c r="E75">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>3.16</v>
       </c>
       <c r="F75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>155237.7429357217</v>
       </c>
       <c r="M75">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="N75">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R75">
+        <f t="shared" si="12"/>
+        <v>2.6608524989875482E-2</v>
       </c>
       <c r="S75">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>96.378696316105206</v>
       </c>
       <c r="T75">
         <f>SUM($S$2:S75)</f>
-        <v>1999.0099009901046</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.35">
+        <v>3527.0678931557054</v>
+      </c>
+      <c r="U75">
+        <f t="shared" si="14"/>
+        <v>3.3566913709508714</v>
+      </c>
+      <c r="W75">
+        <f t="shared" si="15"/>
+        <v>164900.3772652616</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>74</v>
       </c>
@@ -3311,34 +4269,46 @@
         <v>50019.065617954053</v>
       </c>
       <c r="D76">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>26</v>
       </c>
       <c r="E76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>3.08</v>
       </c>
       <c r="F76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>154058.7221032985</v>
       </c>
       <c r="M76">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="N76">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R76">
+        <f t="shared" si="12"/>
+        <v>2.4197072451914336E-2</v>
       </c>
       <c r="S76">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>88.541475567731482</v>
       </c>
       <c r="T76">
         <f>SUM($S$2:S76)</f>
-        <v>2013.8613861386195</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.35">
+        <v>3615.609368723437</v>
+      </c>
+      <c r="U76">
+        <f t="shared" si="14"/>
+        <v>3.2150250100425009</v>
+      </c>
+      <c r="W76">
+        <f t="shared" si="15"/>
+        <v>160812.54694067923</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>75</v>
       </c>
@@ -3349,34 +4319,46 @@
         <v>50912.26321827466</v>
       </c>
       <c r="D77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>25</v>
       </c>
       <c r="E77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="F77">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>152736.78965482398</v>
       </c>
       <c r="M77">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="N77">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R77">
+        <f t="shared" si="12"/>
+        <v>2.1785217703255054E-2</v>
       </c>
       <c r="S77">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>80.70294763458881</v>
       </c>
       <c r="T77">
         <f>SUM($S$2:S77)</f>
-        <v>2028.7128712871345</v>
-      </c>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.35">
+        <v>3696.3123163580258</v>
+      </c>
+      <c r="U77">
+        <f t="shared" si="14"/>
+        <v>3.0859002938271587</v>
+      </c>
+      <c r="W77">
+        <f t="shared" si="15"/>
+        <v>157110.16802467941</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>76</v>
       </c>
@@ -3387,34 +4369,46 @@
         <v>51805.460818595267</v>
       </c>
       <c r="D78">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>24</v>
       </c>
       <c r="E78">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2.92</v>
       </c>
       <c r="F78">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>151271.94559029819</v>
       </c>
       <c r="M78">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="N78">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R78">
+        <f t="shared" si="12"/>
+        <v>1.9418605498321296E-2</v>
       </c>
       <c r="S78">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>73.011457968554112</v>
       </c>
       <c r="T78">
         <f>SUM($S$2:S78)</f>
-        <v>2043.5643564356494</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.35">
+        <v>3769.32377432658</v>
+      </c>
+      <c r="U78">
+        <f t="shared" si="14"/>
+        <v>2.9690819610774719</v>
+      </c>
+      <c r="W78">
+        <f t="shared" si="15"/>
+        <v>153814.65920179698</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>77</v>
       </c>
@@ -3425,34 +4419,46 @@
         <v>52707.932485168298</v>
       </c>
       <c r="D79">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>23</v>
       </c>
       <c r="E79">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2.84</v>
       </c>
       <c r="F79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>149690.52825787794</v>
       </c>
       <c r="M79">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="N79">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R79">
+        <f t="shared" si="12"/>
+        <v>1.7136859204780735E-2</v>
       </c>
       <c r="S79">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>65.595782514547295</v>
       </c>
       <c r="T79">
         <f>SUM($S$2:S79)</f>
-        <v>2058.4158415841644</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.35">
+        <v>3834.9195568411274</v>
+      </c>
+      <c r="U79">
+        <f t="shared" si="14"/>
+        <v>2.8641287090541963</v>
+      </c>
+      <c r="W79">
+        <f t="shared" si="15"/>
+        <v>150962.30262566081</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>78</v>
       </c>
@@ -3463,34 +4469,46 @@
         <v>53616.689941809127</v>
       </c>
       <c r="D80">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="E80">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2.76</v>
       </c>
       <c r="F80">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>147982.06423939319</v>
       </c>
       <c r="M80">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="N80">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R80">
+        <f t="shared" si="12"/>
+        <v>1.4972746563574486E-2</v>
       </c>
       <c r="S80">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>58.562416430626982</v>
       </c>
       <c r="T80">
         <f>SUM($S$2:S80)</f>
-        <v>2073.2673267326791</v>
-      </c>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.35">
+        <v>3893.4819732717542</v>
+      </c>
+      <c r="U80">
+        <f t="shared" si="14"/>
+        <v>2.7704288427651935</v>
+      </c>
+      <c r="W80">
+        <f t="shared" si="15"/>
+        <v>148541.22426838646</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>79</v>
       </c>
@@ -3501,34 +4519,46 @@
         <v>54525.447398449956</v>
       </c>
       <c r="D81">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="E81">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2.6799999999999997</v>
       </c>
       <c r="F81">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>146128.19902784587</v>
       </c>
       <c r="M81">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="N81">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R81">
+        <f t="shared" si="12"/>
+        <v>1.2951759566589173E-2</v>
       </c>
       <c r="S81">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>51.994208690424713</v>
       </c>
       <c r="T81">
         <f>SUM($S$2:S81)</f>
-        <v>2088.1188118811938</v>
-      </c>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.35">
+        <v>3945.476181962179</v>
+      </c>
+      <c r="U81">
+        <f t="shared" si="14"/>
+        <v>2.6872381088605133</v>
+      </c>
+      <c r="W81">
+        <f t="shared" si="15"/>
+        <v>146522.86015178406</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>80</v>
       </c>
@@ -3539,34 +4569,46 @@
         <v>55434.204855090793</v>
       </c>
       <c r="D82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="E82">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2.6</v>
       </c>
       <c r="F82">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>144128.93262323606</v>
       </c>
       <c r="M82">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="N82">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R82">
+        <f t="shared" si="12"/>
+        <v>1.1092083467945555E-2</v>
       </c>
       <c r="S82">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>45.950261369832958</v>
       </c>
       <c r="T82">
         <f>SUM($S$2:S82)</f>
-        <v>2102.9702970297085</v>
-      </c>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.35">
+        <v>3991.4264433320118</v>
+      </c>
+      <c r="U82">
+        <f t="shared" si="14"/>
+        <v>2.6137176906687811</v>
+      </c>
+      <c r="W82">
+        <f t="shared" si="15"/>
+        <v>144889.36189790803</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>81</v>
       </c>
@@ -3577,34 +4619,46 @@
         <v>56342.96231173163</v>
       </c>
       <c r="D83">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="E83">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2.52</v>
       </c>
       <c r="F83">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>141984.26502556371</v>
       </c>
       <c r="M83">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="N83">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R83">
+        <f t="shared" si="12"/>
+        <v>9.4049077376886937E-3</v>
       </c>
       <c r="S83">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>40.466940246498154</v>
       </c>
       <c r="T83">
         <f>SUM($S$2:S83)</f>
-        <v>2117.8217821782232</v>
-      </c>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.35">
+        <v>4031.8933835785101</v>
+      </c>
+      <c r="U83">
+        <f t="shared" si="14"/>
+        <v>2.5489705862743839</v>
+      </c>
+      <c r="W83">
+        <f t="shared" si="15"/>
+        <v>143616.55367617009</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>82</v>
       </c>
@@ -3615,34 +4669,46 @@
         <v>57260.595174070229</v>
       </c>
       <c r="D84">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>18</v>
       </c>
       <c r="E84">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2.44</v>
       </c>
       <c r="F84">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>139715.85222473135</v>
       </c>
       <c r="M84">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="N84">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R84">
+        <f t="shared" si="12"/>
+        <v>7.8950158300894139E-3</v>
       </c>
       <c r="S84">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>35.559791546800497</v>
       </c>
       <c r="T84">
         <f>SUM($S$2:S84)</f>
-        <v>2132.6732673267379</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.35">
+        <v>4067.4531751253107</v>
+      </c>
+      <c r="U84">
+        <f t="shared" si="14"/>
+        <v>2.4920749197995029</v>
+      </c>
+      <c r="W84">
+        <f t="shared" si="15"/>
+        <v>142697.69312609287</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>83</v>
       </c>
@@ -3653,34 +4719,46 @@
         <v>58184.15316074877</v>
       </c>
       <c r="D85">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="E85">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2.3600000000000003</v>
       </c>
       <c r="F85">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>137314.60145936711</v>
       </c>
       <c r="M85">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="N85">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R85">
+        <f t="shared" si="12"/>
+        <v>6.5615814774676604E-3</v>
       </c>
       <c r="S85">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>31.226129900779799</v>
       </c>
       <c r="T85">
         <f>SUM($S$2:S85)</f>
-        <v>2147.5247524752526</v>
-      </c>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.35">
+        <v>4098.6793050260903</v>
+      </c>
+      <c r="U85">
+        <f t="shared" si="14"/>
+        <v>2.4421131119582555</v>
+      </c>
+      <c r="W85">
+        <f t="shared" si="15"/>
+        <v>142092.28334205196</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>84</v>
       </c>
@@ -3691,34 +4769,46 @@
         <v>59107.711147427333</v>
       </c>
       <c r="D86">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="E86">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2.2800000000000002</v>
       </c>
       <c r="F86">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>134765.58141613434</v>
       </c>
       <c r="M86">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="N86">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R86">
+        <f t="shared" si="12"/>
+        <v>5.3990966513188061E-3</v>
       </c>
       <c r="S86">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>27.448054215796024</v>
       </c>
       <c r="T86">
         <f>SUM($S$2:S86)</f>
-        <v>2162.3762376237673</v>
-      </c>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.35">
+        <v>4126.1273592418866</v>
+      </c>
+      <c r="U86">
+        <f t="shared" si="14"/>
+        <v>2.3981962252129816</v>
+      </c>
+      <c r="W86">
+        <f t="shared" si="15"/>
+        <v>141751.8897547395</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>85</v>
       </c>
@@ -3729,34 +4819,46 @@
         <v>60031.269134105882</v>
       </c>
       <c r="D87">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="E87">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="F87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>132068.79209503296</v>
       </c>
       <c r="M87">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="N87">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R87">
+        <f t="shared" si="12"/>
+        <v>4.3983595980427196E-3</v>
       </c>
       <c r="S87">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>24.195658792648739</v>
       </c>
       <c r="T87">
         <f>SUM($S$2:S87)</f>
-        <v>2177.227722772282</v>
-      </c>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.35">
+        <v>4150.3230180345354</v>
+      </c>
+      <c r="U87">
+        <f t="shared" si="14"/>
+        <v>2.3594831711447437</v>
+      </c>
+      <c r="W87">
+        <f t="shared" si="15"/>
+        <v>141642.76926438371</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>86</v>
       </c>
@@ -3767,34 +4869,46 @@
         <v>60954.82712078443</v>
       </c>
       <c r="D88">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
       <c r="E88">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2.12</v>
       </c>
       <c r="F88">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>129224.233496063</v>
       </c>
       <c r="M88">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="N88">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R88">
+        <f t="shared" si="12"/>
+        <v>3.5474592846231421E-3</v>
       </c>
       <c r="S88">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>21.430232774035115</v>
       </c>
       <c r="T88">
         <f>SUM($S$2:S88)</f>
-        <v>2192.0792079207968</v>
-      </c>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.35">
+        <v>4171.7532508085706</v>
+      </c>
+      <c r="U88">
+        <f t="shared" si="14"/>
+        <v>2.3251947987062871</v>
+      </c>
+      <c r="W88">
+        <f t="shared" si="15"/>
+        <v>141731.84697728889</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>87</v>
       </c>
@@ -3805,34 +4919,46 @@
         <v>61886.211128846291</v>
       </c>
       <c r="D89">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="E89">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2.04</v>
       </c>
       <c r="F89">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>126247.87070284644</v>
       </c>
       <c r="M89">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="N89">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R89">
+        <f t="shared" si="12"/>
+        <v>2.8327037741601186E-3</v>
       </c>
       <c r="S89">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>19.107277365030289</v>
       </c>
       <c r="T89">
         <f>SUM($S$2:S89)</f>
-        <v>2206.9306930693115</v>
-      </c>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.35">
+        <v>4190.8605281736009</v>
+      </c>
+      <c r="U89">
+        <f t="shared" si="14"/>
+        <v>2.2946231549222387</v>
+      </c>
+      <c r="W89">
+        <f t="shared" si="15"/>
+        <v>142005.53302665704</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>88</v>
       </c>
@@ -3843,34 +4969,46 @@
         <v>62823.880994434883</v>
       </c>
       <c r="D90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="E90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.96</v>
       </c>
       <c r="F90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>123134.80674909237</v>
       </c>
       <c r="M90">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="N90">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R90">
+        <f t="shared" si="12"/>
+        <v>2.2394530294842902E-3</v>
       </c>
       <c r="S90">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>17.179212444833844</v>
       </c>
       <c r="T90">
         <f>SUM($S$2:S90)</f>
-        <v>2221.7821782178262</v>
-      </c>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.35">
+        <v>4208.0397406184347</v>
+      </c>
+      <c r="U90">
+        <f t="shared" si="14"/>
+        <v>2.2671364150105044</v>
+      </c>
+      <c r="W90">
+        <f t="shared" si="15"/>
+        <v>142430.30833476965</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>89</v>
       </c>
@@ -3881,34 +5019,46 @@
         <v>63761.550860023468</v>
       </c>
       <c r="D91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="E91">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.88</v>
       </c>
       <c r="F91">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>119871.71561684411</v>
       </c>
       <c r="M91">
-        <v>89</v>
+        <v>11</v>
       </c>
       <c r="N91">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R91">
+        <f t="shared" si="12"/>
+        <v>1.752830049356854E-3</v>
       </c>
       <c r="S91">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>15.597687759419678</v>
       </c>
       <c r="T91">
         <f>SUM($S$2:S91)</f>
-        <v>2236.6336633663409</v>
-      </c>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.35">
+        <v>4223.6374283778541</v>
+      </c>
+      <c r="U91">
+        <f t="shared" si="14"/>
+        <v>2.2421801145954334</v>
+      </c>
+      <c r="W91">
+        <f t="shared" si="15"/>
+        <v>142964.88141410999</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>90</v>
       </c>
@@ -3919,34 +5069,46 @@
         <v>64699.220725612031</v>
       </c>
       <c r="D92">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="E92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.8</v>
       </c>
       <c r="F92">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>116458.59730610166</v>
       </c>
       <c r="M92">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="N92">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R92">
+        <f t="shared" si="12"/>
+        <v>1.3582969233685612E-3</v>
       </c>
       <c r="S92">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>14.315455099957726</v>
       </c>
       <c r="T92">
         <f>SUM($S$2:S92)</f>
-        <v>2251.4851485148556</v>
-      </c>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.35">
+        <v>4237.9528834778121</v>
+      </c>
+      <c r="U92">
+        <f t="shared" si="14"/>
+        <v>2.2192753864355006</v>
+      </c>
+      <c r="W92">
+        <f t="shared" si="15"/>
+        <v>143585.3880779084</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>91</v>
       </c>
@@ -3957,34 +5119,46 @@
         <v>65636.890591200616</v>
       </c>
       <c r="D93">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="E93">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.72</v>
       </c>
       <c r="F93">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>112895.45181686505</v>
       </c>
       <c r="M93">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="N93">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R93">
+        <f t="shared" si="12"/>
+        <v>1.0420934814422591E-3</v>
       </c>
       <c r="S93">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>13.287793913697243</v>
       </c>
       <c r="T93">
         <f>SUM($S$2:S93)</f>
-        <v>2266.3366336633703</v>
-      </c>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.35">
+        <v>4251.2406773915091</v>
+      </c>
+      <c r="U93">
+        <f t="shared" si="14"/>
+        <v>2.1980149161735856</v>
+      </c>
+      <c r="W93">
+        <f t="shared" si="15"/>
+        <v>144270.86457071264</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>92</v>
       </c>
@@ -3995,34 +5169,46 @@
         <v>66580.803695104405</v>
       </c>
       <c r="D94">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="E94">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.6400000000000001</v>
       </c>
       <c r="F94">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>109192.51805997123</v>
       </c>
       <c r="M94">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="N94">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R94">
+        <f t="shared" si="12"/>
+        <v>7.9154515829799694E-4</v>
       </c>
       <c r="S94">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>12.473511863478391</v>
       </c>
       <c r="T94">
         <f>SUM($S$2:S94)</f>
-        <v>2281.188118811885</v>
-      </c>
-    </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.35">
+        <v>4263.7141892549871</v>
+      </c>
+      <c r="U94">
+        <f t="shared" si="14"/>
+        <v>2.1780572971920207</v>
+      </c>
+      <c r="W94">
+        <f t="shared" si="15"/>
+        <v>145016.80534103161</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>93</v>
       </c>
@@ -4033,34 +5219,46 @@
         <v>67531.958033605901</v>
       </c>
       <c r="D95">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="E95">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.56</v>
       </c>
       <c r="F95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>105349.8545324252</v>
       </c>
       <c r="M95">
-        <v>93</v>
+        <v>7</v>
       </c>
       <c r="N95">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R95">
+        <f t="shared" si="12"/>
+        <v>5.9525324197758534E-4</v>
       </c>
       <c r="S95">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>11.835563135437054</v>
       </c>
       <c r="T95">
         <f>SUM($S$2:S95)</f>
-        <v>2296.0396039603997</v>
-      </c>
-    </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.35">
+        <v>4275.5497523904241</v>
+      </c>
+      <c r="U95">
+        <f t="shared" si="14"/>
+        <v>2.1591203961753216</v>
+      </c>
+      <c r="W95">
+        <f t="shared" si="15"/>
+        <v>145809.62798401437</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>94</v>
       </c>
@@ -4071,34 +5269,49 @@
         <v>68483.112372107396</v>
       </c>
       <c r="D96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
       <c r="E96">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.48</v>
       </c>
       <c r="F96">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>101355.00631071895</v>
       </c>
       <c r="M96">
-        <v>94</v>
+        <v>6</v>
       </c>
       <c r="N96">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="Q96">
+        <v>0.3</v>
+      </c>
+      <c r="R96">
+        <f t="shared" si="12"/>
+        <v>4.4318484119380076E-4</v>
       </c>
       <c r="S96">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>86.34134083288977</v>
       </c>
       <c r="T96">
         <f>SUM($S$2:S96)</f>
-        <v>2310.8910891089145</v>
-      </c>
-    </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.35">
+        <v>4361.8910932233139</v>
+      </c>
+      <c r="U96">
+        <f t="shared" si="14"/>
+        <v>2.0209742508426976</v>
+      </c>
+      <c r="W96">
+        <f t="shared" si="15"/>
+        <v>138402.60672159601</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>95</v>
       </c>
@@ -4109,34 +5322,49 @@
         <v>69434.266710608877</v>
       </c>
       <c r="D97">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
       <c r="E97">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.4</v>
       </c>
       <c r="F97">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>97207.973394852423</v>
       </c>
       <c r="M97">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="N97">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="Q97">
+        <v>0.4</v>
+      </c>
+      <c r="R97">
+        <f t="shared" si="12"/>
+        <v>3.2668190561999186E-4</v>
       </c>
       <c r="S97">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>110.9627062922749</v>
       </c>
       <c r="T97">
         <f>SUM($S$2:S97)</f>
-        <v>2325.7425742574292</v>
-      </c>
-    </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.35">
+        <v>4472.8537995155884</v>
+      </c>
+      <c r="U97">
+        <f t="shared" si="14"/>
+        <v>1.8434339207750585</v>
+      </c>
+      <c r="W97">
+        <f t="shared" si="15"/>
+        <v>127997.48251847885</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>96</v>
       </c>
@@ -4147,34 +5375,49 @@
         <v>70385.421049110373</v>
       </c>
       <c r="D98">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="E98">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.32</v>
       </c>
       <c r="F98">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>92908.755784825698</v>
       </c>
       <c r="M98">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="N98">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="Q98">
+        <v>0.3</v>
+      </c>
+      <c r="R98">
+        <f t="shared" si="12"/>
+        <v>2.3840882014648405E-4</v>
       </c>
       <c r="S98">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>85.675818764485967</v>
       </c>
       <c r="T98">
         <f>SUM($S$2:S98)</f>
-        <v>2340.5940594059439</v>
-      </c>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.35">
+        <v>4558.5296182800748</v>
+      </c>
+      <c r="U98">
+        <f t="shared" si="14"/>
+        <v>1.7063526107518803</v>
+      </c>
+      <c r="W98">
+        <f t="shared" si="15"/>
+        <v>120102.34696601983</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>97</v>
       </c>
@@ -4185,34 +5428,46 @@
         <v>71340.797195344814</v>
       </c>
       <c r="D99">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="E99">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.24</v>
       </c>
       <c r="F99">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>88462.588522227568</v>
       </c>
       <c r="M99">
-        <v>97</v>
+        <v>3</v>
       </c>
       <c r="N99">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R99">
+        <f t="shared" si="12"/>
+        <v>1.722568939053681E-4</v>
       </c>
       <c r="S99">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>10.460825004202349</v>
       </c>
       <c r="T99">
         <f>SUM($S$2:S99)</f>
-        <v>2355.4455445544586</v>
-      </c>
-    </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.35">
+        <v>4568.9904432842768</v>
+      </c>
+      <c r="U99">
+        <f t="shared" si="14"/>
+        <v>1.6896152907451572</v>
+      </c>
+      <c r="W99">
+        <f t="shared" si="15"/>
+        <v>120538.50179520382</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>98</v>
       </c>
@@ -4223,34 +5478,46 @@
         <v>72304.862022308938</v>
       </c>
       <c r="D100">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="E100">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.1599999999999999</v>
       </c>
       <c r="F100">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>83873.639945878356</v>
       </c>
       <c r="M100">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="N100">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="R100">
+        <f t="shared" si="12"/>
+        <v>1.2322191684730198E-4</v>
       </c>
       <c r="S100">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f t="shared" si="13"/>
+        <v>10.301461328763633</v>
       </c>
       <c r="T100">
         <f>SUM($S$2:S100)</f>
-        <v>2370.2970297029733</v>
-      </c>
-    </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.35">
+        <v>4579.2919046130401</v>
+      </c>
+      <c r="U100">
+        <f t="shared" si="14"/>
+        <v>1.6731329526191359</v>
+      </c>
+      <c r="W100">
+        <f t="shared" si="15"/>
+        <v>120975.64728410498</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>99</v>
       </c>
@@ -4261,34 +5528,50 @@
         <v>73268.926849273048</v>
       </c>
       <c r="D101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="E101">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1.08</v>
       </c>
       <c r="F101">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>79130.440997214901</v>
       </c>
       <c r="M101">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="N101">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="P101">
+        <f>1/2</f>
+        <v>0.5</v>
+      </c>
+      <c r="R101">
+        <f t="shared" si="12"/>
+        <v>8.726826950457601E-5</v>
       </c>
       <c r="S101">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f>($J$3*N101+$J$4*O101+$J$5*P101+$J$6*Q101+$J$7*R101)*5000</f>
+        <v>210.18461197489978</v>
       </c>
       <c r="T101">
         <f>SUM($S$2:S101)</f>
-        <v>2385.148514851488</v>
-      </c>
-    </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.35">
+        <v>4789.4765165879398</v>
+      </c>
+      <c r="U101">
+        <f t="shared" si="14"/>
+        <v>1.3368375734592963</v>
+      </c>
+      <c r="W101">
+        <f t="shared" si="15"/>
+        <v>97948.654379148866</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>100</v>
       </c>
@@ -4299,34 +5582,50 @@
         <v>74232.991676237172</v>
       </c>
       <c r="D102">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E102">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F102">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>74232.991676237172</v>
       </c>
       <c r="M102">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N102">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
+        <f t="shared" si="11"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="P102">
+        <f>1/2</f>
+        <v>0.5</v>
+      </c>
+      <c r="R102">
+        <f t="shared" si="12"/>
+        <v>6.1190193011377187E-5</v>
       </c>
       <c r="S102">
-        <f t="shared" si="9"/>
-        <v>14.851485148514852</v>
+        <f>($J$3*N102+$J$4*O102+$J$5*P102+$J$6*Q102+$J$7*R102)*5000</f>
+        <v>210.09985822629687</v>
       </c>
       <c r="T102">
         <f>SUM($S$2:S102)</f>
-        <v>2400.0000000000027</v>
-      </c>
-    </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.35">
+        <v>4999.5763748142363</v>
+      </c>
+      <c r="U102">
+        <f t="shared" si="14"/>
+        <v>1.0006778002972221</v>
+      </c>
+      <c r="W102">
+        <f t="shared" si="15"/>
+        <v>74283.306820059006</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" x14ac:dyDescent="0.35">
       <c r="E103" t="s">
         <v>6</v>
       </c>
@@ -4334,27 +5633,8 @@
         <f>MAX(F1:F102)</f>
         <v>160065.31395662154</v>
       </c>
-      <c r="M103">
-        <v>101</v>
-      </c>
-      <c r="N103">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-      <c r="P103">
-        <f>1/2</f>
-        <v>0.5</v>
-      </c>
-      <c r="S103">
-        <f t="shared" si="9"/>
-        <v>64.851485148514854</v>
-      </c>
-      <c r="T103">
-        <f>SUM($S$2:S103)</f>
-        <v>2464.8514851485174</v>
-      </c>
-    </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.35">
+    </row>
+    <row r="104" spans="1:23" x14ac:dyDescent="0.35">
       <c r="E104" t="s">
         <v>7</v>
       </c>
@@ -4362,37 +5642,24 @@
         <f>MATCH(F103,F2:F102,0)-1</f>
         <v>64</v>
       </c>
-      <c r="M104">
-        <v>102</v>
-      </c>
-      <c r="N104">
-        <f t="shared" si="8"/>
-        <v>9.9009900990099011E-3</v>
-      </c>
-      <c r="P104">
-        <f>1/2</f>
-        <v>0.5</v>
-      </c>
-      <c r="S104">
-        <f t="shared" si="9"/>
-        <v>64.851485148514854</v>
-      </c>
-      <c r="T104">
-        <f>SUM($S$2:S104)</f>
-        <v>2529.7029702970322</v>
-      </c>
-    </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="S105">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T105">
-        <f>SUM($S$2:S105)</f>
-        <v>2529.7029702970322</v>
-      </c>
-    </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="V104" t="s">
+        <v>22</v>
+      </c>
+      <c r="W104">
+        <f>MAX(W2:W102)</f>
+        <v>233259.36872387634</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="V105" t="s">
+        <v>23</v>
+      </c>
+      <c r="W105">
+        <f>MATCH(W104,W2:W102,0)</f>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" x14ac:dyDescent="0.35">
       <c r="N106" s="1"/>
     </row>
   </sheetData>

--- a/Manual Trading/Day 2/optimal_allocation.xlsx
+++ b/Manual Trading/Day 2/optimal_allocation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92c4f7ffed9c6980/Python/IntaraTradingAlgorithm/Manual Trading/Day 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="187" documentId="11_3C91D1A4D360D04F55E2DCF0505ED87656CD3EF8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57673FE8-D3E5-455D-915B-B7607BA1847A}"/>
+  <xr:revisionPtr revIDLastSave="194" documentId="11_3C91D1A4D360D04F55E2DCF0505ED87656CD3EF8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CB8C1A3-FC9A-4A5C-8E4A-D217AB925818}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -143,7 +143,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -164,6 +164,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -560,15 +564,15 @@
       </c>
       <c r="S2">
         <f>($J$3*N2+$J$4*O2+$J$5*P2+$J$6*Q2+$J$7*R2)*5000</f>
-        <v>59.900990264374464</v>
+        <v>34.900990283454988</v>
       </c>
       <c r="T2">
         <f>SUM($S$2:S2)</f>
-        <v>59.900990264374464</v>
+        <v>34.900990283454988</v>
       </c>
       <c r="U2">
         <f>(5000-T2)/5000*8+1</f>
-        <v>8.9041584155770011</v>
+        <v>8.9441584155464717</v>
       </c>
       <c r="W2">
         <f>U2*C2</f>
@@ -619,15 +623,15 @@
       </c>
       <c r="S3">
         <f t="shared" ref="S3:S66" si="5">($J$3*N3+$J$4*O3+$J$5*P3+$J$6*Q3+$J$7*R3)*5000</f>
-        <v>59.90099041105649</v>
+        <v>34.900990447061865</v>
       </c>
       <c r="T3">
         <f>SUM($S$2:S3)</f>
-        <v>119.80198067543095</v>
+        <v>69.801980730516846</v>
       </c>
       <c r="U3">
         <f t="shared" ref="U3:U66" si="6">(5000-T3)/5000*8+1</f>
-        <v>8.8083168309193098</v>
+        <v>8.8883168308311724</v>
       </c>
       <c r="W3">
         <f t="shared" ref="W3:W66" si="7">U3*C3</f>
@@ -660,7 +664,7 @@
         <v>16</v>
       </c>
       <c r="J4">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="M4">
         <v>98</v>
@@ -675,19 +679,19 @@
       </c>
       <c r="S4">
         <f t="shared" si="5"/>
-        <v>9.9009906819896703</v>
+        <v>9.9009907492565681</v>
       </c>
       <c r="T4">
         <f>SUM($S$2:S4)</f>
-        <v>129.70297135742064</v>
+        <v>79.70297147977341</v>
       </c>
       <c r="U4">
         <f t="shared" si="6"/>
-        <v>8.7924752458281272</v>
+        <v>8.8724752456323621</v>
       </c>
       <c r="W4">
         <f t="shared" si="7"/>
-        <v>1848.7645482645378</v>
+        <v>1865.585882344428</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.35">
@@ -716,7 +720,7 @@
         <v>21</v>
       </c>
       <c r="J5">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="M5">
         <v>97</v>
@@ -731,19 +735,19 @@
       </c>
       <c r="S5">
         <f t="shared" si="5"/>
-        <v>9.900991177322279</v>
+        <v>9.9009913017429394</v>
       </c>
       <c r="T5">
         <f>SUM($S$2:S5)</f>
-        <v>139.60396253474292</v>
+        <v>89.603962781516344</v>
       </c>
       <c r="U5">
         <f t="shared" si="6"/>
-        <v>8.7766336599444124</v>
+        <v>8.8566336595495745</v>
       </c>
       <c r="W5">
         <f t="shared" si="7"/>
-        <v>3690.867181300142</v>
+        <v>3724.5098493762057</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
@@ -772,7 +776,7 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>0.05</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="M6">
         <v>96</v>
@@ -787,19 +791,19 @@
       </c>
       <c r="S6">
         <f t="shared" si="5"/>
-        <v>9.9009920736718282</v>
+        <v>9.9009923015174355</v>
       </c>
       <c r="T6">
         <f>SUM($S$2:S6)</f>
-        <v>149.50495460841475</v>
+        <v>99.504955083033778</v>
       </c>
       <c r="U6">
         <f t="shared" si="6"/>
-        <v>8.7607920726265363</v>
+        <v>8.8407920718671456</v>
       </c>
       <c r="W6">
         <f t="shared" si="7"/>
-        <v>5839.3271907263661</v>
+        <v>5892.6495578081503</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.35">
@@ -828,7 +832,7 @@
         <v>17</v>
       </c>
       <c r="J7">
-        <v>0.65</v>
+        <v>0.72499999999999998</v>
       </c>
       <c r="M7">
         <v>95</v>
@@ -843,19 +847,19 @@
       </c>
       <c r="S7">
         <f t="shared" si="5"/>
-        <v>9.9009936791330784</v>
+        <v>9.9009940922242148</v>
       </c>
       <c r="T7">
         <f>SUM($S$2:S7)</f>
-        <v>159.40594828754783</v>
+        <v>109.40594917525799</v>
       </c>
       <c r="U7">
         <f t="shared" si="6"/>
-        <v>8.7449504827399238</v>
+        <v>8.8249504813195863</v>
       </c>
       <c r="W7">
         <f t="shared" si="7"/>
-        <v>8743.1524533562097</v>
+        <v>8823.1360033180754</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.35">
@@ -893,19 +897,19 @@
       </c>
       <c r="S8">
         <f t="shared" si="5"/>
-        <v>9.9009965252987335</v>
+        <v>9.900997266793599</v>
       </c>
       <c r="T8">
         <f>SUM($S$2:S8)</f>
-        <v>169.30694481284655</v>
+        <v>119.30694644205158</v>
       </c>
       <c r="U8">
         <f t="shared" si="6"/>
-        <v>8.7291088882994465</v>
+        <v>8.8091088856927175</v>
       </c>
       <c r="W8">
         <f t="shared" si="7"/>
-        <v>11636.418821426591</v>
+        <v>11743.063553127547</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.35">
@@ -943,19 +947,19 @@
       </c>
       <c r="S9">
         <f t="shared" si="5"/>
-        <v>9.9010015193639607</v>
+        <v>9.9010028370971206</v>
       </c>
       <c r="T9">
         <f>SUM($S$2:S9)</f>
-        <v>179.20794633221053</v>
+        <v>129.20794927914869</v>
       </c>
       <c r="U9">
         <f t="shared" si="6"/>
-        <v>8.7132672858684632</v>
+        <v>8.7932672811533621</v>
       </c>
       <c r="W9">
         <f t="shared" si="7"/>
-        <v>14656.878030163449</v>
+        <v>14791.448695200444</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.35">
@@ -993,19 +997,19 @@
       </c>
       <c r="S10">
         <f t="shared" si="5"/>
-        <v>9.9010101925265257</v>
+        <v>9.9010125110092151</v>
       </c>
       <c r="T10">
         <f>SUM($S$2:S10)</f>
-        <v>189.10895652473704</v>
+        <v>139.10896179015791</v>
       </c>
       <c r="U10">
         <f t="shared" si="6"/>
-        <v>8.6974256695604204</v>
+        <v>8.777425661135748</v>
       </c>
       <c r="W10">
         <f t="shared" si="7"/>
-        <v>18287.787897587426</v>
+        <v>18456.001221083679</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.35">
@@ -1043,19 +1047,19 @@
       </c>
       <c r="S11">
         <f t="shared" si="5"/>
-        <v>9.9010251007300383</v>
+        <v>9.9010291393900545</v>
       </c>
       <c r="T11">
         <f>SUM($S$2:S11)</f>
-        <v>199.00998162546708</v>
+        <v>149.00999092954797</v>
       </c>
       <c r="U11">
         <f t="shared" si="6"/>
-        <v>8.6815840293992537</v>
+        <v>8.7615840145127244</v>
       </c>
       <c r="W11">
         <f t="shared" si="7"/>
-        <v>21905.373848778439</v>
+        <v>22107.229820669381</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.35">
@@ -1093,19 +1097,19 @@
       </c>
       <c r="S12">
         <f t="shared" si="5"/>
-        <v>9.9010504632698506</v>
+        <v>9.9010574283767667</v>
       </c>
       <c r="T12">
         <f>SUM($S$2:S12)</f>
-        <v>208.91103208873693</v>
+        <v>158.91104835792473</v>
       </c>
       <c r="U12">
         <f t="shared" si="6"/>
-        <v>8.6657423486580214</v>
+        <v>8.7457423226273221</v>
       </c>
       <c r="W12">
         <f t="shared" si="7"/>
-        <v>25509.635804403737</v>
+        <v>25745.134405471039</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.35">
@@ -1143,19 +1147,19 @@
       </c>
       <c r="S13">
         <f t="shared" si="5"/>
-        <v>9.9010931678594432</v>
+        <v>9.9011050604190061</v>
       </c>
       <c r="T13">
         <f>SUM($S$2:S13)</f>
-        <v>218.81212525659637</v>
+        <v>168.81215341834374</v>
       </c>
       <c r="U13">
         <f t="shared" si="6"/>
-        <v>8.6499005995894471</v>
+        <v>8.7299005545306496</v>
       </c>
       <c r="W13">
         <f t="shared" si="7"/>
-        <v>29561.629766123966</v>
+        <v>29835.035110156554</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.35">
@@ -1193,19 +1197,19 @@
       </c>
       <c r="S14">
         <f t="shared" si="5"/>
-        <v>9.9011643326586043</v>
+        <v>9.901184436541147</v>
       </c>
       <c r="T14">
         <f>SUM($S$2:S14)</f>
-        <v>228.71328958925497</v>
+        <v>178.71333785488488</v>
       </c>
       <c r="U14">
         <f t="shared" si="6"/>
-        <v>8.6340587366571917</v>
+        <v>8.7140586594321832</v>
       </c>
       <c r="W14">
         <f t="shared" si="7"/>
-        <v>33722.844698075627</v>
+        <v>34035.307822764029</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.35">
@@ -1243,19 +1247,19 @@
       </c>
       <c r="S15">
         <f t="shared" si="5"/>
-        <v>9.9012817031526783</v>
+        <v>9.9013153497845376</v>
       </c>
       <c r="T15">
         <f>SUM($S$2:S15)</f>
-        <v>238.61457129240765</v>
+        <v>188.61465320466942</v>
       </c>
       <c r="U15">
         <f t="shared" si="6"/>
-        <v>8.618216685932147</v>
+        <v>8.6982165548725288</v>
       </c>
       <c r="W15">
         <f t="shared" si="7"/>
-        <v>37868.590046203237</v>
+        <v>38220.110824927498</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.35">
@@ -1293,19 +1297,19 @@
       </c>
       <c r="S16">
         <f t="shared" si="5"/>
-        <v>9.901473282852189</v>
+        <v>9.9015290348339917</v>
       </c>
       <c r="T16">
         <f>SUM($S$2:S16)</f>
-        <v>248.51604457525983</v>
+        <v>198.51618223950342</v>
       </c>
       <c r="U16">
         <f t="shared" si="6"/>
-        <v>8.6023743286795842</v>
+        <v>8.6823741084167949</v>
       </c>
       <c r="W16">
         <f t="shared" si="7"/>
-        <v>42080.950784086606</v>
+        <v>42472.292367843991</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.35">
@@ -1343,19 +1347,19 @@
       </c>
       <c r="S17">
         <f t="shared" si="5"/>
-        <v>9.9017827612523153</v>
+        <v>9.9018742222802878</v>
       </c>
       <c r="T17">
         <f>SUM($S$2:S17)</f>
-        <v>258.41782733651212</v>
+        <v>208.41805646178372</v>
       </c>
       <c r="U17">
         <f t="shared" si="6"/>
-        <v>8.5865314762615803</v>
+        <v>8.6665311096611468</v>
       </c>
       <c r="W17">
         <f t="shared" si="7"/>
-        <v>46670.501093057079</v>
+        <v>47105.324279618573</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.35">
@@ -1393,19 +1397,19 @@
       </c>
       <c r="S18">
         <f t="shared" si="5"/>
-        <v>9.9022775212144865</v>
+        <v>9.9024260699303994</v>
       </c>
       <c r="T18">
         <f>SUM($S$2:S18)</f>
-        <v>268.32010485772662</v>
+        <v>218.32048253171411</v>
       </c>
       <c r="U18">
         <f t="shared" si="6"/>
-        <v>8.5706878322276374</v>
+        <v>8.6506872279492573</v>
       </c>
       <c r="W18">
         <f t="shared" si="7"/>
-        <v>51242.824491225321</v>
+        <v>51721.128575403069</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.35">
@@ -1443,19 +1447,19 @@
       </c>
       <c r="S19">
         <f t="shared" si="5"/>
-        <v>9.9030602921930324</v>
+        <v>9.9032991606372409</v>
       </c>
       <c r="T19">
         <f>SUM($S$2:S19)</f>
-        <v>278.22316514991962</v>
+        <v>228.22378169235134</v>
       </c>
       <c r="U19">
         <f t="shared" si="6"/>
-        <v>8.5548429357601279</v>
+        <v>8.6348419492922375</v>
       </c>
       <c r="W19">
         <f t="shared" si="7"/>
-        <v>55797.91668216019</v>
+        <v>56319.700463024317</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.35">
@@ -1493,19 +1497,19 @@
       </c>
       <c r="S20">
         <f t="shared" si="5"/>
-        <v>9.9042858759311851</v>
+        <v>9.904666157883641</v>
       </c>
       <c r="T20">
         <f>SUM($S$2:S20)</f>
-        <v>288.1274510258508</v>
+        <v>238.12844785023498</v>
       </c>
       <c r="U20">
         <f t="shared" si="6"/>
-        <v>8.5389960783586396</v>
+        <v>8.618994483439625</v>
       </c>
       <c r="W20">
         <f t="shared" si="7"/>
-        <v>60486.134737452725</v>
+        <v>61052.804901498508</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.35">
@@ -1543,19 +1547,19 @@
       </c>
       <c r="S21">
         <f t="shared" si="5"/>
-        <v>9.906184814869647</v>
+        <v>9.9067842051611539</v>
       </c>
       <c r="T21">
         <f>SUM($S$2:S21)</f>
-        <v>298.03363584072042</v>
+        <v>248.03523205539614</v>
       </c>
       <c r="U21">
         <f t="shared" si="6"/>
-        <v>8.5231461826548482</v>
+        <v>8.6031436287113667</v>
       </c>
       <c r="W21">
         <f t="shared" si="7"/>
-        <v>65405.016854277455</v>
+        <v>66018.902172620772</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.35">
@@ -1593,19 +1597,19 @@
       </c>
       <c r="S22">
         <f t="shared" si="5"/>
-        <v>9.9090964021791681</v>
+        <v>9.9100317448525459</v>
       </c>
       <c r="T22">
         <f>SUM($S$2:S22)</f>
-        <v>307.94273224289958</v>
+        <v>257.94526380024865</v>
       </c>
       <c r="U22">
         <f t="shared" si="6"/>
-        <v>8.5072916284113624</v>
+        <v>8.5872875779196036</v>
       </c>
       <c r="W22">
         <f t="shared" si="7"/>
-        <v>70305.148301473964</v>
+        <v>70966.243199750592</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.35">
@@ -1643,19 +1647,19 @@
       </c>
       <c r="S23">
         <f t="shared" si="5"/>
-        <v>9.9135140379510798</v>
+        <v>9.9149591078289081</v>
       </c>
       <c r="T23">
         <f>SUM($S$2:S23)</f>
-        <v>317.85624628085066</v>
+        <v>267.86022290807756</v>
       </c>
       <c r="U23">
         <f t="shared" si="6"/>
-        <v>8.4914300059506402</v>
+        <v>8.5714236433470745</v>
       </c>
       <c r="W23">
         <f t="shared" si="7"/>
-        <v>75186.499493085881</v>
+        <v>75894.794983167332</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.35">
@@ -1693,19 +1697,19 @@
       </c>
       <c r="S24">
         <f t="shared" si="5"/>
-        <v>9.9201465960307775</v>
+        <v>9.9223569610716478</v>
       </c>
       <c r="T24">
         <f>SUM($S$2:S24)</f>
-        <v>327.77639287688146</v>
+        <v>277.78257986914923</v>
       </c>
       <c r="U24">
         <f t="shared" si="6"/>
-        <v>8.4755577713969892</v>
+        <v>8.5555478722093614</v>
       </c>
       <c r="W24">
         <f t="shared" si="7"/>
-        <v>80195.731388413056</v>
+        <v>80952.597757742726</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.35">
@@ -1743,19 +1747,19 @@
       </c>
       <c r="S25">
         <f t="shared" si="5"/>
-        <v>9.9300001375924687</v>
+        <v>9.9333474497366119</v>
       </c>
       <c r="T25">
         <f>SUM($S$2:S25)</f>
-        <v>337.70639301447392</v>
+        <v>287.71592731888586</v>
       </c>
       <c r="U25">
         <f t="shared" si="6"/>
-        <v>8.4596697711768414</v>
+        <v>8.539654516289783</v>
       </c>
       <c r="W25">
         <f t="shared" si="7"/>
-        <v>85381.75906484283</v>
+        <v>86189.029138122074</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.35">
@@ -1793,19 +1797,19 @@
       </c>
       <c r="S26">
         <f t="shared" si="5"/>
-        <v>9.9444849223834879</v>
+        <v>9.9495035558496721</v>
       </c>
       <c r="T26">
         <f>SUM($S$2:S26)</f>
-        <v>347.6508779368574</v>
+        <v>297.66543087473553</v>
       </c>
       <c r="U26">
         <f t="shared" si="6"/>
-        <v>8.443758595301027</v>
+        <v>8.5237353106004221</v>
       </c>
       <c r="W26">
         <f t="shared" si="7"/>
-        <v>90547.493912783495</v>
+        <v>91405.132257130099</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.35">
@@ -1843,19 +1847,19 @@
       </c>
       <c r="S27">
         <f t="shared" si="5"/>
-        <v>9.9655531272125533</v>
+        <v>9.9730027073897816</v>
       </c>
       <c r="T27">
         <f>SUM($S$2:S27)</f>
-        <v>357.61643106406996</v>
+        <v>307.63843358212534</v>
       </c>
       <c r="U27">
         <f t="shared" si="6"/>
-        <v>8.4278137102974888</v>
+        <v>8.5077785062685987</v>
       </c>
       <c r="W27">
         <f t="shared" si="7"/>
-        <v>95692.77247336146</v>
+        <v>96600.724795253976</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.35">
@@ -1893,19 +1897,19 @@
       </c>
       <c r="S28">
         <f t="shared" si="5"/>
-        <v>9.995872849892125</v>
+        <v>10.006820859609306</v>
       </c>
       <c r="T28">
         <f>SUM($S$2:S28)</f>
-        <v>367.61230391396208</v>
+        <v>317.64525444173466</v>
       </c>
       <c r="U28">
         <f t="shared" si="6"/>
-        <v>8.4118203137376604</v>
+        <v>8.4917675928932255</v>
       </c>
       <c r="W28">
         <f t="shared" si="7"/>
-        <v>100921.08934188592</v>
+        <v>101880.25943841338</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.35">
@@ -1943,19 +1947,19 @@
       </c>
       <c r="S29">
         <f t="shared" si="5"/>
-        <v>10.039043686938896</v>
+        <v>10.054972947084549</v>
       </c>
       <c r="T29">
         <f>SUM($S$2:S29)</f>
-        <v>377.65134760090098</v>
+        <v>327.7002273888192</v>
       </c>
       <c r="U29">
         <f t="shared" si="6"/>
-        <v>8.3957578438385578</v>
+        <v>8.4756796361778903</v>
       </c>
       <c r="W29">
         <f t="shared" si="7"/>
-        <v>106324.40040801784</v>
+        <v>107336.53496550152</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.35">
@@ -1993,19 +1997,19 @@
       </c>
       <c r="S30">
         <f t="shared" si="5"/>
-        <v>10.099858226296876</v>
+        <v>10.122804548676145</v>
       </c>
       <c r="T30">
         <f>SUM($S$2:S30)</f>
-        <v>387.75120582719785</v>
+        <v>337.82303193749533</v>
       </c>
       <c r="U30">
         <f t="shared" si="6"/>
-        <v>8.379598070676483</v>
+        <v>8.4594831489000075</v>
       </c>
       <c r="W30">
         <f t="shared" si="7"/>
-        <v>111705.00214095257</v>
+        <v>112769.91751740911</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.35">
@@ -2043,19 +2047,19 @@
       </c>
       <c r="S31">
         <f t="shared" si="5"/>
-        <v>10.184611974899774</v>
+        <v>10.21733757596399</v>
       </c>
       <c r="T31">
         <f>SUM($S$2:S31)</f>
-        <v>397.93581780209763</v>
+        <v>348.04036951345932</v>
       </c>
       <c r="U31">
         <f t="shared" si="6"/>
-        <v>8.363302691516644</v>
+        <v>8.4431354087784651</v>
       </c>
       <c r="W31">
         <f t="shared" si="7"/>
-        <v>117062.16384614442</v>
+        <v>118179.59208868141</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.35">
@@ -2093,19 +2097,19 @@
       </c>
       <c r="S32">
         <f t="shared" si="5"/>
-        <v>10.301461328763633</v>
+        <v>10.34766954758137</v>
       </c>
       <c r="T32">
         <f>SUM($S$2:S32)</f>
-        <v>408.23727913086128</v>
+        <v>358.38803906104067</v>
       </c>
       <c r="U32">
         <f t="shared" si="6"/>
-        <v>8.3468203533906209</v>
+        <v>8.4265791375023333</v>
       </c>
       <c r="W32">
         <f t="shared" si="7"/>
-        <v>122433.71826473183</v>
+        <v>123603.64454679254</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.35">
@@ -2143,19 +2147,19 @@
       </c>
       <c r="S33">
         <f t="shared" si="5"/>
-        <v>10.460825004202349</v>
+        <v>10.525421339416862</v>
       </c>
       <c r="T33">
         <f>SUM($S$2:S33)</f>
-        <v>418.69810413506366</v>
+        <v>368.91346040045755</v>
       </c>
       <c r="U33">
         <f t="shared" si="6"/>
-        <v>8.3300830333838984</v>
+        <v>8.4097384633592682</v>
       </c>
       <c r="W33">
         <f t="shared" si="7"/>
-        <v>128006.69632336484</v>
+        <v>129230.74515871266</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.35">
@@ -2193,19 +2197,19 @@
       </c>
       <c r="S34">
         <f t="shared" si="5"/>
-        <v>10.675818764485975</v>
+        <v>10.765222072040906</v>
       </c>
       <c r="T34">
         <f>SUM($S$2:S34)</f>
-        <v>429.37392289954965</v>
+        <v>379.67868247249845</v>
       </c>
       <c r="U34">
         <f t="shared" si="6"/>
-        <v>8.3130017233607205</v>
+        <v>8.3925141080440024</v>
       </c>
       <c r="W34">
         <f t="shared" si="7"/>
-        <v>133550.76635591651</v>
+        <v>134828.15571088294</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.35">
@@ -2243,19 +2247,19 @@
       </c>
       <c r="S35">
         <f t="shared" si="5"/>
-        <v>10.962706292274875</v>
+        <v>11.085212006882372</v>
       </c>
       <c r="T35">
         <f>SUM($S$2:S35)</f>
-        <v>440.33662919182456</v>
+        <v>390.76389447938084</v>
       </c>
       <c r="U35">
         <f t="shared" si="6"/>
-        <v>8.2954613932930812</v>
+        <v>8.3747777688329919</v>
       </c>
       <c r="W35">
         <f t="shared" si="7"/>
-        <v>139063.27920288598</v>
+        <v>140392.92137155251</v>
       </c>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.35">
@@ -2293,19 +2297,19 @@
       </c>
       <c r="S36">
         <f t="shared" si="5"/>
-        <v>11.341340832889752</v>
+        <v>11.50753514833743</v>
       </c>
       <c r="T36">
         <f>SUM($S$2:S36)</f>
-        <v>451.67797002471428</v>
+        <v>402.27142962771825</v>
       </c>
       <c r="U36">
         <f t="shared" si="6"/>
-        <v>8.2773152479604573</v>
+        <v>8.3563657125956503</v>
       </c>
       <c r="W36">
         <f t="shared" si="7"/>
-        <v>144540.70962276385</v>
+        <v>145921.11014057614</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.35">
@@ -2343,19 +2347,19 @@
       </c>
       <c r="S37">
         <f t="shared" si="5"/>
-        <v>11.835563135437054</v>
+        <v>12.058783101178648</v>
       </c>
       <c r="T37">
         <f>SUM($S$2:S37)</f>
-        <v>463.51353316015133</v>
+        <v>414.33021272889687</v>
       </c>
       <c r="U37">
         <f t="shared" si="6"/>
-        <v>8.2583783469437577</v>
+        <v>8.3370716596337644</v>
       </c>
       <c r="W37">
         <f t="shared" si="7"/>
-        <v>150179.26865395653</v>
+        <v>151610.31281919702</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.35">
@@ -2393,19 +2397,19 @@
       </c>
       <c r="S38">
         <f t="shared" si="5"/>
-        <v>12.473511863478391</v>
+        <v>12.77034129784014</v>
       </c>
       <c r="T38">
         <f>SUM($S$2:S38)</f>
-        <v>475.98704502362972</v>
+        <v>427.10055402673703</v>
       </c>
       <c r="U38">
         <f t="shared" si="6"/>
-        <v>8.2384207279621933</v>
+        <v>8.3166391135572209</v>
       </c>
       <c r="W38">
         <f t="shared" si="7"/>
-        <v>155808.99127208273</v>
+        <v>157288.29515336271</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.35">
@@ -2443,19 +2447,19 @@
       </c>
       <c r="S39">
         <f t="shared" si="5"/>
-        <v>13.287793913697243</v>
+        <v>13.678578969238091</v>
       </c>
       <c r="T39">
         <f>SUM($S$2:S39)</f>
-        <v>489.27483893732699</v>
+        <v>440.77913299597515</v>
       </c>
       <c r="U39">
         <f t="shared" si="6"/>
-        <v>8.2171602577002751</v>
+        <v>8.2947533872064394</v>
       </c>
       <c r="W39">
         <f t="shared" si="7"/>
-        <v>161384.09156806383</v>
+        <v>162908.01179409822</v>
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.35">
@@ -2493,19 +2497,19 @@
       </c>
       <c r="S40">
         <f t="shared" si="5"/>
-        <v>14.315455099957726</v>
+        <v>14.824816446220934</v>
       </c>
       <c r="T40">
         <f>SUM($S$2:S40)</f>
-        <v>503.59029403728471</v>
+        <v>455.6039494421961</v>
       </c>
       <c r="U40">
         <f t="shared" si="6"/>
-        <v>8.1942555295403459</v>
+        <v>8.2710336808924865</v>
       </c>
       <c r="W40">
         <f t="shared" si="7"/>
-        <v>166894.77292002251</v>
+        <v>168458.53574007866</v>
       </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.35">
@@ -2543,19 +2547,19 @@
       </c>
       <c r="S41">
         <f t="shared" si="5"/>
-        <v>15.597687759419678</v>
+        <v>16.254999027928498</v>
       </c>
       <c r="T41">
         <f>SUM($S$2:S41)</f>
-        <v>519.18798179670443</v>
+        <v>471.85894847012457</v>
       </c>
       <c r="U41">
         <f t="shared" si="6"/>
-        <v>8.1692992291252722</v>
+        <v>8.2450256824478014</v>
       </c>
       <c r="W41">
         <f t="shared" si="7"/>
-        <v>172424.07418306134</v>
+        <v>174022.38307579388</v>
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.35">
@@ -2593,19 +2597,19 @@
       </c>
       <c r="S42">
         <f t="shared" si="5"/>
-        <v>17.179212444833844</v>
+        <v>18.019007330890453</v>
       </c>
       <c r="T42">
         <f>SUM($S$2:S42)</f>
-        <v>536.3671942415383</v>
+        <v>489.87795580101505</v>
       </c>
       <c r="U42">
         <f t="shared" si="6"/>
-        <v>8.1418124892135388</v>
+        <v>8.2161952707183765</v>
       </c>
       <c r="W42">
         <f t="shared" si="7"/>
-        <v>177981.2126749421</v>
+        <v>179607.23116553068</v>
       </c>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.35">
@@ -2643,19 +2647,19 @@
       </c>
       <c r="S43">
         <f t="shared" si="5"/>
-        <v>19.107277365030289</v>
+        <v>20.169541280340329</v>
       </c>
       <c r="T43">
         <f>SUM($S$2:S43)</f>
-        <v>555.47447160656861</v>
+        <v>510.0474970813554</v>
       </c>
       <c r="U43">
         <f t="shared" si="6"/>
-        <v>8.1112408454294886</v>
+        <v>8.1839240046698301</v>
       </c>
       <c r="W43">
         <f t="shared" si="7"/>
-        <v>183427.15041440984</v>
+        <v>185070.80334453887</v>
       </c>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.35">
@@ -2693,19 +2697,19 @@
       </c>
       <c r="S44">
         <f t="shared" si="5"/>
-        <v>21.430232774035115</v>
+        <v>22.760530005768789</v>
       </c>
       <c r="T44">
         <f>SUM($S$2:S44)</f>
-        <v>576.90470438060368</v>
+        <v>532.80802708712417</v>
       </c>
       <c r="U44">
         <f t="shared" si="6"/>
-        <v>8.0769524729910334</v>
+        <v>8.1475071566606019</v>
       </c>
       <c r="W44">
         <f t="shared" si="7"/>
-        <v>188740.14689804835</v>
+        <v>190388.85058977731</v>
       </c>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.35">
@@ -2743,19 +2747,19 @@
       </c>
       <c r="S45">
         <f t="shared" si="5"/>
-        <v>24.195658792648739</v>
+        <v>25.84504364191476</v>
       </c>
       <c r="T45">
         <f>SUM($S$2:S45)</f>
-        <v>601.10036317325239</v>
+        <v>558.65307072903897</v>
       </c>
       <c r="U45">
         <f t="shared" si="6"/>
-        <v>8.0382394189227959</v>
+        <v>8.1061550868335388</v>
       </c>
       <c r="W45">
         <f t="shared" si="7"/>
-        <v>193894.72021971096</v>
+        <v>195532.95077515926</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.35">
@@ -2793,19 +2797,19 @@
       </c>
       <c r="S46">
         <f t="shared" si="5"/>
-        <v>27.448054215796024</v>
+        <v>29.472715460040572</v>
       </c>
       <c r="T46">
         <f>SUM($S$2:S46)</f>
-        <v>628.54841738904838</v>
+        <v>588.12578618907958</v>
       </c>
       <c r="U46">
         <f t="shared" si="6"/>
-        <v>7.9943225321775229</v>
+        <v>8.0589987420974722</v>
       </c>
       <c r="W46">
         <f t="shared" si="7"/>
-        <v>199046.90463890505</v>
+        <v>200657.24739609618</v>
       </c>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.35">
@@ -2843,19 +2847,19 @@
       </c>
       <c r="S47">
         <f t="shared" si="5"/>
-        <v>31.226129900779799</v>
+        <v>33.686722954830174</v>
       </c>
       <c r="T47">
         <f>SUM($S$2:S47)</f>
-        <v>659.77454728982821</v>
+        <v>621.81250914390978</v>
       </c>
       <c r="U47">
         <f t="shared" si="6"/>
-        <v>7.9443607243362759</v>
+        <v>8.0050999853697444</v>
       </c>
       <c r="W47">
         <f t="shared" si="7"/>
-        <v>203984.27043819285</v>
+        <v>205543.84889626974</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.35">
@@ -2893,19 +2897,19 @@
       </c>
       <c r="S48">
         <f t="shared" si="5"/>
-        <v>35.559791546800497</v>
+        <v>38.520422483084026</v>
       </c>
       <c r="T48">
         <f>SUM($S$2:S48)</f>
-        <v>695.33433883662872</v>
+        <v>660.33293162699385</v>
       </c>
       <c r="U48">
         <f t="shared" si="6"/>
-        <v>7.8874650578613945</v>
+        <v>7.9434673093968104</v>
       </c>
       <c r="W48">
         <f t="shared" si="7"/>
-        <v>208660.4546634919</v>
+        <v>210141.97695003595</v>
       </c>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.35">
@@ -2943,19 +2947,19 @@
       </c>
       <c r="S49">
         <f t="shared" si="5"/>
-        <v>40.466940246498154</v>
+        <v>43.99378064813142</v>
       </c>
       <c r="T49">
         <f>SUM($S$2:S49)</f>
-        <v>735.80127908312693</v>
+        <v>704.32671227512526</v>
       </c>
       <c r="U49">
         <f t="shared" si="6"/>
-        <v>7.8227179534669968</v>
+        <v>7.8730772603597998</v>
       </c>
       <c r="W49">
         <f t="shared" si="7"/>
-        <v>213034.28381583677</v>
+        <v>214405.70727008715</v>
       </c>
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.35">
@@ -2993,19 +2997,19 @@
       </c>
       <c r="S50">
         <f t="shared" si="5"/>
-        <v>45.950261369832958</v>
+        <v>50.109792670312537</v>
       </c>
       <c r="T50">
         <f>SUM($S$2:S50)</f>
-        <v>781.75154045295994</v>
+        <v>754.43650494543783</v>
       </c>
       <c r="U50">
         <f t="shared" si="6"/>
-        <v>7.7491975352752638</v>
+        <v>7.7929015920872988</v>
       </c>
       <c r="W50">
         <f t="shared" si="7"/>
-        <v>217129.37885249098</v>
+        <v>218353.94883741316</v>
       </c>
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.35">
@@ -3043,19 +3047,19 @@
       </c>
       <c r="S51">
         <f t="shared" si="5"/>
-        <v>51.994208690424713</v>
+        <v>56.85111852789565</v>
       </c>
       <c r="T51">
         <f>SUM($S$2:S51)</f>
-        <v>833.74574914338461</v>
+        <v>811.2876234733335</v>
       </c>
       <c r="U51">
         <f t="shared" si="6"/>
-        <v>7.6660068013705853</v>
+        <v>7.7019398024426655</v>
       </c>
       <c r="W51">
         <f t="shared" si="7"/>
-        <v>220935.50553149288</v>
+        <v>221971.10019802832</v>
       </c>
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.35">
@@ -3093,19 +3097,19 @@
       </c>
       <c r="S52">
         <f t="shared" si="5"/>
-        <v>58.562416430626982</v>
+        <v>64.177196391967414</v>
       </c>
       <c r="T52">
         <f>SUM($S$2:S52)</f>
-        <v>892.30816557401158</v>
+        <v>875.46481986530091</v>
       </c>
       <c r="U52">
         <f t="shared" si="6"/>
-        <v>7.5723069350815813</v>
+        <v>7.5992562882155177</v>
       </c>
       <c r="W52">
         <f t="shared" si="7"/>
-        <v>224297.14586935507</v>
+        <v>225095.40497886937</v>
       </c>
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.35">
@@ -3143,19 +3147,19 @@
       </c>
       <c r="S53">
         <f t="shared" si="5"/>
-        <v>65.595782514547295</v>
+        <v>72.022104716340067</v>
       </c>
       <c r="T53">
         <f>SUM($S$2:S53)</f>
-        <v>957.90394808855888</v>
+        <v>947.48692458164101</v>
       </c>
       <c r="U53">
         <f t="shared" si="6"/>
-        <v>7.467353683058306</v>
+        <v>7.4840209206693746</v>
       </c>
       <c r="W53">
         <f t="shared" si="7"/>
-        <v>227166.41916149142</v>
+        <v>227673.45777866719</v>
       </c>
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.35">
@@ -3193,19 +3197,19 @@
       </c>
       <c r="S54">
         <f t="shared" si="5"/>
-        <v>73.011457968554112</v>
+        <v>80.29343503042459</v>
       </c>
       <c r="T54">
         <f>SUM($S$2:S54)</f>
-        <v>1030.9154060571129</v>
+        <v>1027.7803596120657</v>
       </c>
       <c r="U54">
         <f t="shared" si="6"/>
-        <v>7.3505353503086193</v>
+        <v>7.3555514246206952</v>
       </c>
       <c r="W54">
         <f t="shared" si="7"/>
-        <v>229497.20014101223</v>
+        <v>229653.81118435241</v>
       </c>
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.35">
@@ -3243,19 +3247,19 @@
       </c>
       <c r="S55">
         <f t="shared" si="5"/>
-        <v>80.70294763458881</v>
+        <v>88.872404273309456</v>
       </c>
       <c r="T55">
         <f>SUM($S$2:S55)</f>
-        <v>1111.6183536917017</v>
+        <v>1116.6527638853752</v>
       </c>
       <c r="U55">
         <f t="shared" si="6"/>
-        <v>7.221410634093278</v>
+        <v>7.2133555777833998</v>
       </c>
       <c r="W55">
         <f t="shared" si="7"/>
-        <v>231360.03874439103</v>
+        <v>231101.97030951444</v>
       </c>
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.35">
@@ -3293,19 +3297,19 @@
       </c>
       <c r="S56">
         <f t="shared" si="5"/>
-        <v>88.541475567731482</v>
+        <v>97.615377737199367</v>
       </c>
       <c r="T56">
         <f>SUM($S$2:S56)</f>
-        <v>1200.1598292594331</v>
+        <v>1214.2681416225746</v>
       </c>
       <c r="U56">
         <f t="shared" si="6"/>
-        <v>7.0797442731849074</v>
+        <v>7.0571709734038803</v>
       </c>
       <c r="W56">
         <f t="shared" si="7"/>
-        <v>232637.2537046714</v>
+        <v>231895.50509547369</v>
       </c>
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.35">
@@ -3343,19 +3347,19 @@
       </c>
       <c r="S57">
         <f t="shared" si="5"/>
-        <v>96.378696316105206</v>
+        <v>106.35689318730851</v>
       </c>
       <c r="T57">
         <f>SUM($S$2:S57)</f>
-        <v>1296.5385255755382</v>
+        <v>1320.6250348098831</v>
       </c>
       <c r="U57">
         <f t="shared" si="6"/>
-        <v>6.9255383590791393</v>
+        <v>6.8869999443041872</v>
       </c>
       <c r="W57">
         <f t="shared" si="7"/>
-        <v>233259.36872387634</v>
+        <v>231961.35464382442</v>
       </c>
     </row>
     <row r="58" spans="1:23" x14ac:dyDescent="0.35">
@@ -3393,19 +3397,19 @@
       </c>
       <c r="S58">
         <f t="shared" si="5"/>
-        <v>104.05074474649177</v>
+        <v>114.91417797504739</v>
       </c>
       <c r="T58">
         <f>SUM($S$2:S58)</f>
-        <v>1400.58927032203</v>
+        <v>1435.5392127849304</v>
       </c>
       <c r="U58">
         <f t="shared" si="6"/>
-        <v>6.7590571674847526</v>
+        <v>6.7031372595441114</v>
       </c>
       <c r="W58">
         <f t="shared" si="7"/>
-        <v>233204.59867226522</v>
+        <v>231275.2201560098</v>
       </c>
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.35">
@@ -3443,19 +3447,19 @@
       </c>
       <c r="S59">
         <f t="shared" si="5"/>
-        <v>111.38351844320732</v>
+        <v>123.09304094446087</v>
       </c>
       <c r="T59">
         <f>SUM($S$2:S59)</f>
-        <v>1511.9727887652373</v>
+        <v>1558.6322537293913</v>
       </c>
       <c r="U59">
         <f t="shared" si="6"/>
-        <v>6.5808435379756203</v>
+        <v>6.5061883940329741</v>
       </c>
       <c r="W59">
         <f t="shared" si="7"/>
-        <v>232466.99269638766</v>
+        <v>229829.81454414711</v>
       </c>
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.35">
@@ -3493,19 +3497,19 @@
       </c>
       <c r="S60">
         <f t="shared" si="5"/>
-        <v>118.19898603884479</v>
+        <v>130.69490864728726</v>
       </c>
       <c r="T60">
         <f>SUM($S$2:S60)</f>
-        <v>1630.1717748040821</v>
+        <v>1689.3271623766786</v>
       </c>
       <c r="U60">
         <f t="shared" si="6"/>
-        <v>6.3917251603134693</v>
+        <v>6.2970765401973141</v>
       </c>
       <c r="W60">
         <f t="shared" si="7"/>
-        <v>231162.29074288468</v>
+        <v>227739.24120728316</v>
       </c>
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.35">
@@ -3543,19 +3547,19 @@
       </c>
       <c r="S61">
         <f t="shared" si="5"/>
-        <v>124.32222129740725</v>
+        <v>137.52467105106848</v>
       </c>
       <c r="T61">
         <f>SUM($S$2:S61)</f>
-        <v>1754.4939961014893</v>
+        <v>1826.8518334277471</v>
       </c>
       <c r="U61">
         <f t="shared" si="6"/>
-        <v>6.192809606237617</v>
+        <v>6.0770370665156053</v>
       </c>
       <c r="W61">
         <f t="shared" si="7"/>
-        <v>229176.90297609786</v>
+        <v>224892.5161161428</v>
       </c>
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.35">
@@ -3593,19 +3597,19 @@
       </c>
       <c r="S62">
         <f t="shared" si="5"/>
-        <v>129.58878569758997</v>
+        <v>143.39891595896461</v>
       </c>
       <c r="T62">
         <f>SUM($S$2:S62)</f>
-        <v>1884.0827817990794</v>
+        <v>1970.2507493867117</v>
       </c>
       <c r="U62">
         <f t="shared" si="6"/>
-        <v>5.9854675491214726</v>
+        <v>5.8475988009812614</v>
       </c>
       <c r="W62">
         <f t="shared" si="7"/>
-        <v>226537.98640760884</v>
+        <v>221319.92978364378</v>
       </c>
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.35">
@@ -3643,19 +3647,19 @@
       </c>
       <c r="S63">
         <f t="shared" si="5"/>
-        <v>133.85203012368021</v>
+        <v>148.15407320344988</v>
       </c>
       <c r="T63">
         <f>SUM($S$2:S63)</f>
-        <v>2017.9348119227595</v>
+        <v>2118.4048225901615</v>
       </c>
       <c r="U63">
         <f t="shared" si="6"/>
-        <v>5.7713043009235845</v>
+        <v>5.6105522838557418</v>
       </c>
       <c r="W63">
         <f t="shared" si="7"/>
-        <v>223286.3873082441</v>
+        <v>217067.04151186187</v>
       </c>
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.35">
@@ -3693,19 +3697,19 @@
       </c>
       <c r="S64">
         <f t="shared" si="5"/>
-        <v>136.98986564103308</v>
+        <v>151.65396666511268</v>
       </c>
       <c r="T64">
         <f>SUM($S$2:S64)</f>
-        <v>2154.9246775637926</v>
+        <v>2270.0587892552744</v>
       </c>
       <c r="U64">
         <f t="shared" si="6"/>
-        <v>5.5521205158979319</v>
+        <v>5.3679059371915612</v>
       </c>
       <c r="W64">
         <f t="shared" si="7"/>
-        <v>219503.26471811259</v>
+        <v>212220.33537266043</v>
       </c>
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.35">
@@ -3743,19 +3747,19 @@
       </c>
       <c r="S65">
         <f t="shared" si="5"/>
-        <v>138.91056802903873</v>
+        <v>153.79628855942667</v>
       </c>
       <c r="T65">
         <f>SUM($S$2:S65)</f>
-        <v>2293.8352455928311</v>
+        <v>2423.855077814701</v>
       </c>
       <c r="U65">
         <f t="shared" si="6"/>
-        <v>5.32986360705147</v>
+        <v>5.1218318754964782</v>
       </c>
       <c r="W65">
         <f t="shared" si="7"/>
-        <v>215297.12041241006</v>
+        <v>206893.78478128032</v>
       </c>
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.35">
@@ -3793,19 +3797,19 @@
       </c>
       <c r="S66">
         <f t="shared" si="5"/>
-        <v>139.55723122947555</v>
+        <v>154.51756674452929</v>
       </c>
       <c r="T66">
         <f>SUM($S$2:S66)</f>
-        <v>2433.3924768223069</v>
+        <v>2578.3726445592301</v>
       </c>
       <c r="U66">
         <f t="shared" si="6"/>
-        <v>5.1065720370843088</v>
+        <v>4.8746037687052315</v>
       </c>
       <c r="W66">
         <f t="shared" si="7"/>
-        <v>210666.25163866093</v>
+        <v>201096.64501338493</v>
       </c>
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.35">
@@ -3827,35 +3831,35 @@
         <v>3.8000000000000003</v>
       </c>
       <c r="F67">
-        <f t="shared" ref="F67:F103" si="10">E67*C67</f>
+        <f t="shared" ref="F67:F102" si="10">E67*C67</f>
         <v>160030.93566754152</v>
       </c>
       <c r="M67">
         <v>35</v>
       </c>
       <c r="N67">
-        <f t="shared" ref="N67:N104" si="11">1/101</f>
+        <f t="shared" ref="N67:N102" si="11">1/101</f>
         <v>9.9009900990099011E-3</v>
       </c>
       <c r="R67">
-        <f t="shared" ref="R67:R103" si="12">_xlfn.NORM.DIST(M67,36,10,FALSE)</f>
+        <f t="shared" ref="R67:R102" si="12">_xlfn.NORM.DIST(M67,36,10,FALSE)</f>
         <v>3.9695254747701178E-2</v>
       </c>
       <c r="S67">
-        <f t="shared" ref="S67:S104" si="13">($J$3*N67+$J$4*O67+$J$5*P67+$J$6*Q67+$J$7*R67)*5000</f>
-        <v>138.91056802903873</v>
+        <f t="shared" ref="S67:S100" si="13">($J$3*N67+$J$4*O67+$J$5*P67+$J$6*Q67+$J$7*R67)*5000</f>
+        <v>153.79628855942667</v>
       </c>
       <c r="T67">
         <f>SUM($S$2:S67)</f>
-        <v>2572.3030448513455</v>
+        <v>2732.1689331186567</v>
       </c>
       <c r="U67">
         <f t="shared" ref="U67:U102" si="14">(5000-T67)/5000*8+1</f>
-        <v>4.8843151282378479</v>
+        <v>4.6285297070101494</v>
       </c>
       <c r="W67">
-        <f t="shared" ref="W67:W104" si="15">U67*C67</f>
-        <v>205695.13685974493</v>
+        <f t="shared" ref="W67:W102" si="15">U67*C67</f>
+        <v>194923.14204680157</v>
       </c>
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.35">
@@ -3893,19 +3897,19 @@
       </c>
       <c r="S68">
         <f t="shared" si="13"/>
-        <v>136.98986564103308</v>
+        <v>151.65396666511268</v>
       </c>
       <c r="T68">
         <f>SUM($S$2:S68)</f>
-        <v>2709.2929104923787</v>
+        <v>2883.8228997837696</v>
       </c>
       <c r="U68">
         <f t="shared" si="14"/>
-        <v>4.6651313432121935</v>
+        <v>4.3858833603459688</v>
       </c>
       <c r="W68">
         <f t="shared" si="15"/>
-        <v>200474.04239157413</v>
+        <v>188473.95754158607</v>
       </c>
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.35">
@@ -3943,19 +3947,19 @@
       </c>
       <c r="S69">
         <f t="shared" si="13"/>
-        <v>133.85203012368021</v>
+        <v>148.15407320344988</v>
       </c>
       <c r="T69">
         <f>SUM($S$2:S69)</f>
-        <v>2843.1449406160591</v>
+        <v>3031.9769729872196</v>
       </c>
       <c r="U69">
         <f t="shared" si="14"/>
-        <v>4.4509680950143053</v>
+        <v>4.1488368432204492</v>
       </c>
       <c r="W69">
         <f t="shared" si="15"/>
-        <v>195129.61148308232</v>
+        <v>181884.23373133663</v>
       </c>
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.35">
@@ -3993,19 +3997,19 @@
       </c>
       <c r="S70">
         <f t="shared" si="13"/>
-        <v>129.58878569758997</v>
+        <v>143.39891595896461</v>
       </c>
       <c r="T70">
         <f>SUM($S$2:S70)</f>
-        <v>2972.7337263136492</v>
+        <v>3175.3758889461842</v>
       </c>
       <c r="U70">
         <f t="shared" si="14"/>
-        <v>4.2436260378981618</v>
+        <v>3.9193985776861053</v>
       </c>
       <c r="W70">
         <f t="shared" si="15"/>
-        <v>189760.56984136545</v>
+        <v>175262.21700381624</v>
       </c>
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.35">
@@ -4043,19 +4047,19 @@
       </c>
       <c r="S71">
         <f t="shared" si="13"/>
-        <v>124.32222129740725</v>
+        <v>137.52467105106848</v>
       </c>
       <c r="T71">
         <f>SUM($S$2:S71)</f>
-        <v>3097.0559476110566</v>
+        <v>3312.9005599972525</v>
       </c>
       <c r="U71">
         <f t="shared" si="14"/>
-        <v>4.0447104838223096</v>
+        <v>3.699359104004396</v>
       </c>
       <c r="W71">
         <f t="shared" si="15"/>
-        <v>184412.1276897068</v>
+        <v>168666.38197872764</v>
       </c>
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.35">
@@ -4093,19 +4097,19 @@
       </c>
       <c r="S72">
         <f t="shared" si="13"/>
-        <v>118.19898603884479</v>
+        <v>130.69490864728726</v>
       </c>
       <c r="T72">
         <f>SUM($S$2:S72)</f>
-        <v>3215.2549336499014</v>
+        <v>3443.5954686445398</v>
       </c>
       <c r="U72">
         <f t="shared" si="14"/>
-        <v>3.8555921061601577</v>
+        <v>3.4902472501687365</v>
       </c>
       <c r="W72">
         <f t="shared" si="15"/>
-        <v>179170.14547650755</v>
+        <v>162192.49607928743</v>
       </c>
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.35">
@@ -4143,19 +4147,19 @@
       </c>
       <c r="S73">
         <f t="shared" si="13"/>
-        <v>111.38351844320732</v>
+        <v>123.09304094446087</v>
       </c>
       <c r="T73">
         <f>SUM($S$2:S73)</f>
-        <v>3326.6384520931088</v>
+        <v>3566.6885095890007</v>
       </c>
       <c r="U73">
         <f t="shared" si="14"/>
-        <v>3.6773784766510258</v>
+        <v>3.2932983846575992</v>
       </c>
       <c r="W73">
         <f t="shared" si="15"/>
-        <v>174112.83378266636</v>
+        <v>155927.79418419025</v>
       </c>
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.35">
@@ -4193,19 +4197,19 @@
       </c>
       <c r="S74">
         <f t="shared" si="13"/>
-        <v>104.05074474649177</v>
+        <v>114.91417797504739</v>
       </c>
       <c r="T74">
         <f>SUM($S$2:S74)</f>
-        <v>3430.6891968396003</v>
+        <v>3681.6026875640482</v>
       </c>
       <c r="U74">
         <f t="shared" si="14"/>
-        <v>3.5108972850566396</v>
+        <v>3.109435699897523</v>
       </c>
       <c r="W74">
         <f t="shared" si="15"/>
-        <v>169339.95161917532</v>
+        <v>149976.38729698368</v>
       </c>
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.35">
@@ -4243,19 +4247,19 @@
       </c>
       <c r="S75">
         <f t="shared" si="13"/>
-        <v>96.378696316105206</v>
+        <v>106.35689318730851</v>
       </c>
       <c r="T75">
         <f>SUM($S$2:S75)</f>
-        <v>3527.0678931557054</v>
+        <v>3787.959580751357</v>
       </c>
       <c r="U75">
         <f t="shared" si="14"/>
-        <v>3.3566913709508714</v>
+        <v>2.9392646707978289</v>
       </c>
       <c r="W75">
         <f t="shared" si="15"/>
-        <v>164900.3772652616</v>
+        <v>144393.928286507</v>
       </c>
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.35">
@@ -4293,19 +4297,19 @@
       </c>
       <c r="S76">
         <f t="shared" si="13"/>
-        <v>88.541475567731482</v>
+        <v>97.615377737199367</v>
       </c>
       <c r="T76">
         <f>SUM($S$2:S76)</f>
-        <v>3615.609368723437</v>
+        <v>3885.5749584885561</v>
       </c>
       <c r="U76">
         <f t="shared" si="14"/>
-        <v>3.2150250100425009</v>
+        <v>2.78308006641831</v>
       </c>
       <c r="W76">
         <f t="shared" si="15"/>
-        <v>160812.54694067923</v>
+        <v>139207.06446219736</v>
       </c>
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.35">
@@ -4343,19 +4347,19 @@
       </c>
       <c r="S77">
         <f t="shared" si="13"/>
-        <v>80.70294763458881</v>
+        <v>88.872404273309456</v>
       </c>
       <c r="T77">
         <f>SUM($S$2:S77)</f>
-        <v>3696.3123163580258</v>
+        <v>3974.4473627618654</v>
       </c>
       <c r="U77">
         <f t="shared" si="14"/>
-        <v>3.0859002938271587</v>
+        <v>2.6408842195810154</v>
       </c>
       <c r="W77">
         <f t="shared" si="15"/>
-        <v>157110.16802467941</v>
+        <v>134453.3925162965</v>
       </c>
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.35">
@@ -4393,19 +4397,19 @@
       </c>
       <c r="S78">
         <f t="shared" si="13"/>
-        <v>73.011457968554112</v>
+        <v>80.29343503042459</v>
       </c>
       <c r="T78">
         <f>SUM($S$2:S78)</f>
-        <v>3769.32377432658</v>
+        <v>4054.7407977922899</v>
       </c>
       <c r="U78">
         <f t="shared" si="14"/>
-        <v>2.9690819610774719</v>
+        <v>2.512414723532336</v>
       </c>
       <c r="W78">
         <f t="shared" si="15"/>
-        <v>153814.65920179698</v>
+        <v>130156.8025200163</v>
       </c>
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.35">
@@ -4443,19 +4447,19 @@
       </c>
       <c r="S79">
         <f t="shared" si="13"/>
-        <v>65.595782514547295</v>
+        <v>72.022104716340067</v>
       </c>
       <c r="T79">
         <f>SUM($S$2:S79)</f>
-        <v>3834.9195568411274</v>
+        <v>4126.7629025086298</v>
       </c>
       <c r="U79">
         <f t="shared" si="14"/>
-        <v>2.8641287090541963</v>
+        <v>2.397179355986192</v>
       </c>
       <c r="W79">
         <f t="shared" si="15"/>
-        <v>150962.30262566081</v>
+        <v>126350.36765015943</v>
       </c>
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.35">
@@ -4493,19 +4497,19 @@
       </c>
       <c r="S80">
         <f t="shared" si="13"/>
-        <v>58.562416430626982</v>
+        <v>64.177196391967414</v>
       </c>
       <c r="T80">
         <f>SUM($S$2:S80)</f>
-        <v>3893.4819732717542</v>
+        <v>4190.9400989005971</v>
       </c>
       <c r="U80">
         <f t="shared" si="14"/>
-        <v>2.7704288427651935</v>
+        <v>2.2944958417590446</v>
       </c>
       <c r="W80">
         <f t="shared" si="15"/>
-        <v>148541.22426838646</v>
+        <v>123023.27212036503</v>
       </c>
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.35">
@@ -4543,19 +4547,19 @@
       </c>
       <c r="S81">
         <f t="shared" si="13"/>
-        <v>51.994208690424713</v>
+        <v>56.85111852789565</v>
       </c>
       <c r="T81">
         <f>SUM($S$2:S81)</f>
-        <v>3945.476181962179</v>
+        <v>4247.7912174284929</v>
       </c>
       <c r="U81">
         <f t="shared" si="14"/>
-        <v>2.6872381088605133</v>
+        <v>2.2035340521144113</v>
       </c>
       <c r="W81">
         <f t="shared" si="15"/>
-        <v>146522.86015178406</v>
+        <v>120148.68004925761</v>
       </c>
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.35">
@@ -4593,19 +4597,19 @@
       </c>
       <c r="S82">
         <f t="shared" si="13"/>
-        <v>45.950261369832958</v>
+        <v>50.109792670312537</v>
       </c>
       <c r="T82">
         <f>SUM($S$2:S82)</f>
-        <v>3991.4264433320118</v>
+        <v>4297.9010100988053</v>
       </c>
       <c r="U82">
         <f t="shared" si="14"/>
-        <v>2.6137176906687811</v>
+        <v>2.1233583838419117</v>
       </c>
       <c r="W82">
         <f t="shared" si="15"/>
-        <v>144889.36189790803</v>
+        <v>117706.68363066704</v>
       </c>
     </row>
     <row r="83" spans="1:23" x14ac:dyDescent="0.35">
@@ -4643,19 +4647,19 @@
       </c>
       <c r="S83">
         <f t="shared" si="13"/>
-        <v>40.466940246498154</v>
+        <v>43.99378064813142</v>
       </c>
       <c r="T83">
         <f>SUM($S$2:S83)</f>
-        <v>4031.8933835785101</v>
+        <v>4341.8947907469365</v>
       </c>
       <c r="U83">
         <f t="shared" si="14"/>
-        <v>2.5489705862743839</v>
+        <v>2.0529683348049019</v>
       </c>
       <c r="W83">
         <f t="shared" si="15"/>
-        <v>143616.55367617009</v>
+        <v>115670.31751509102</v>
       </c>
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.35">
@@ -4693,19 +4697,19 @@
       </c>
       <c r="S84">
         <f t="shared" si="13"/>
-        <v>35.559791546800497</v>
+        <v>38.520422483084026</v>
       </c>
       <c r="T84">
         <f>SUM($S$2:S84)</f>
-        <v>4067.4531751253107</v>
+        <v>4380.4152132300205</v>
       </c>
       <c r="U84">
         <f t="shared" si="14"/>
-        <v>2.4920749197995029</v>
+        <v>1.9913356588319671</v>
       </c>
       <c r="W84">
         <f t="shared" si="15"/>
-        <v>142697.69312609287</v>
+        <v>114025.06501606769</v>
       </c>
     </row>
     <row r="85" spans="1:23" x14ac:dyDescent="0.35">
@@ -4743,19 +4747,19 @@
       </c>
       <c r="S85">
         <f t="shared" si="13"/>
-        <v>31.226129900779799</v>
+        <v>33.686722954830174</v>
       </c>
       <c r="T85">
         <f>SUM($S$2:S85)</f>
-        <v>4098.6793050260903</v>
+        <v>4414.1019361848503</v>
       </c>
       <c r="U85">
         <f t="shared" si="14"/>
-        <v>2.4421131119582555</v>
+        <v>1.9374369021042397</v>
       </c>
       <c r="W85">
         <f t="shared" si="15"/>
-        <v>142092.28334205196</v>
+        <v>112728.12545131971</v>
       </c>
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.35">
@@ -4793,19 +4797,19 @@
       </c>
       <c r="S86">
         <f t="shared" si="13"/>
-        <v>27.448054215796024</v>
+        <v>29.472715460040572</v>
       </c>
       <c r="T86">
         <f>SUM($S$2:S86)</f>
-        <v>4126.1273592418866</v>
+        <v>4443.5746516448908</v>
       </c>
       <c r="U86">
         <f t="shared" si="14"/>
-        <v>2.3981962252129816</v>
+        <v>1.8902805573681749</v>
       </c>
       <c r="W86">
         <f t="shared" si="15"/>
-        <v>141751.8897547395</v>
+        <v>111730.15717251603</v>
       </c>
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.35">
@@ -4843,19 +4847,19 @@
       </c>
       <c r="S87">
         <f t="shared" si="13"/>
-        <v>24.195658792648739</v>
+        <v>25.84504364191476</v>
       </c>
       <c r="T87">
         <f>SUM($S$2:S87)</f>
-        <v>4150.3230180345354</v>
+        <v>4469.4196952868051</v>
       </c>
       <c r="U87">
         <f t="shared" si="14"/>
-        <v>2.3594831711447437</v>
+        <v>1.8489284875411118</v>
       </c>
       <c r="W87">
         <f t="shared" si="15"/>
-        <v>141642.76926438371</v>
+        <v>110993.52364529582</v>
       </c>
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.35">
@@ -4893,19 +4897,19 @@
       </c>
       <c r="S88">
         <f t="shared" si="13"/>
-        <v>21.430232774035115</v>
+        <v>22.760530005768789</v>
       </c>
       <c r="T88">
         <f>SUM($S$2:S88)</f>
-        <v>4171.7532508085706</v>
+        <v>4492.1802252925736</v>
       </c>
       <c r="U88">
         <f t="shared" si="14"/>
-        <v>2.3251947987062871</v>
+        <v>1.8125116395318823</v>
       </c>
       <c r="W88">
         <f t="shared" si="15"/>
-        <v>141731.84697728889</v>
+        <v>110481.33364207543</v>
       </c>
     </row>
     <row r="89" spans="1:23" x14ac:dyDescent="0.35">
@@ -4943,19 +4947,19 @@
       </c>
       <c r="S89">
         <f t="shared" si="13"/>
-        <v>19.107277365030289</v>
+        <v>20.169541280340329</v>
       </c>
       <c r="T89">
         <f>SUM($S$2:S89)</f>
-        <v>4190.8605281736009</v>
+        <v>4512.3497665729137</v>
       </c>
       <c r="U89">
         <f t="shared" si="14"/>
-        <v>2.2946231549222387</v>
+        <v>1.7802403734833381</v>
       </c>
       <c r="W89">
         <f t="shared" si="15"/>
-        <v>142005.53302665704</v>
+        <v>110172.33161348604</v>
       </c>
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.35">
@@ -4993,19 +4997,19 @@
       </c>
       <c r="S90">
         <f t="shared" si="13"/>
-        <v>17.179212444833844</v>
+        <v>18.019007330890453</v>
       </c>
       <c r="T90">
         <f>SUM($S$2:S90)</f>
-        <v>4208.0397406184347</v>
+        <v>4530.3687739038041</v>
       </c>
       <c r="U90">
         <f t="shared" si="14"/>
-        <v>2.2671364150105044</v>
+        <v>1.7514099617539134</v>
       </c>
       <c r="W90">
         <f t="shared" si="15"/>
-        <v>142430.30833476965</v>
+        <v>110030.37100969561</v>
       </c>
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.35">
@@ -5043,19 +5047,19 @@
       </c>
       <c r="S91">
         <f t="shared" si="13"/>
-        <v>15.597687759419678</v>
+        <v>16.254999027928498</v>
       </c>
       <c r="T91">
         <f>SUM($S$2:S91)</f>
-        <v>4223.6374283778541</v>
+        <v>4546.6237729317327</v>
       </c>
       <c r="U91">
         <f t="shared" si="14"/>
-        <v>2.2421801145954334</v>
+        <v>1.7254019633092277</v>
       </c>
       <c r="W91">
         <f t="shared" si="15"/>
-        <v>142964.88141410999</v>
+        <v>110014.30503752567</v>
       </c>
     </row>
     <row r="92" spans="1:23" x14ac:dyDescent="0.35">
@@ -5093,19 +5097,19 @@
       </c>
       <c r="S92">
         <f t="shared" si="13"/>
-        <v>14.315455099957726</v>
+        <v>14.824816446220934</v>
       </c>
       <c r="T92">
         <f>SUM($S$2:S92)</f>
-        <v>4237.9528834778121</v>
+        <v>4561.4485893779538</v>
       </c>
       <c r="U92">
         <f t="shared" si="14"/>
-        <v>2.2192753864355006</v>
+        <v>1.7016822569952739</v>
       </c>
       <c r="W92">
         <f t="shared" si="15"/>
-        <v>143585.3880779084</v>
+        <v>110097.51595019488</v>
       </c>
     </row>
     <row r="93" spans="1:23" x14ac:dyDescent="0.35">
@@ -5143,19 +5147,19 @@
       </c>
       <c r="S93">
         <f t="shared" si="13"/>
-        <v>13.287793913697243</v>
+        <v>13.678578969238091</v>
       </c>
       <c r="T93">
         <f>SUM($S$2:S93)</f>
-        <v>4251.2406773915091</v>
+        <v>4575.1271683471923</v>
       </c>
       <c r="U93">
         <f t="shared" si="14"/>
-        <v>2.1980149161735856</v>
+        <v>1.6797965306444924</v>
       </c>
       <c r="W93">
         <f t="shared" si="15"/>
-        <v>144270.86457071264</v>
+        <v>110256.62109739092</v>
       </c>
     </row>
     <row r="94" spans="1:23" x14ac:dyDescent="0.35">
@@ -5193,19 +5197,19 @@
       </c>
       <c r="S94">
         <f t="shared" si="13"/>
-        <v>12.473511863478391</v>
+        <v>12.77034129784014</v>
       </c>
       <c r="T94">
         <f>SUM($S$2:S94)</f>
-        <v>4263.7141892549871</v>
+        <v>4587.8975096450322</v>
       </c>
       <c r="U94">
         <f t="shared" si="14"/>
-        <v>2.1780572971920207</v>
+        <v>1.6593639845679484</v>
       </c>
       <c r="W94">
         <f t="shared" si="15"/>
-        <v>145016.80534103161</v>
+        <v>110481.78771524483</v>
       </c>
     </row>
     <row r="95" spans="1:23" x14ac:dyDescent="0.35">
@@ -5243,19 +5247,19 @@
       </c>
       <c r="S95">
         <f t="shared" si="13"/>
-        <v>11.835563135437054</v>
+        <v>12.058783101178648</v>
       </c>
       <c r="T95">
         <f>SUM($S$2:S95)</f>
-        <v>4275.5497523904241</v>
+        <v>4599.9562927462111</v>
       </c>
       <c r="U95">
         <f t="shared" si="14"/>
-        <v>2.1591203961753216</v>
+        <v>1.6400699316060621</v>
       </c>
       <c r="W95">
         <f t="shared" si="15"/>
-        <v>145809.62798401437</v>
+        <v>110757.13379339948</v>
       </c>
     </row>
     <row r="96" spans="1:23" x14ac:dyDescent="0.35">
@@ -5296,19 +5300,19 @@
       </c>
       <c r="S96">
         <f t="shared" si="13"/>
-        <v>86.34134083288977</v>
+        <v>49.007535148337425</v>
       </c>
       <c r="T96">
         <f>SUM($S$2:S96)</f>
-        <v>4361.8910932233139</v>
+        <v>4648.9638278945486</v>
       </c>
       <c r="U96">
         <f t="shared" si="14"/>
-        <v>2.0209742508426976</v>
+        <v>1.5616578753687222</v>
       </c>
       <c r="W96">
         <f t="shared" si="15"/>
-        <v>138402.60672159601</v>
+        <v>106947.19176566269</v>
       </c>
     </row>
     <row r="97" spans="1:23" x14ac:dyDescent="0.35">
@@ -5349,19 +5353,19 @@
       </c>
       <c r="S97">
         <f t="shared" si="13"/>
-        <v>110.9627062922749</v>
+        <v>61.085212006882379</v>
       </c>
       <c r="T97">
         <f>SUM($S$2:S97)</f>
-        <v>4472.8537995155884</v>
+        <v>4710.0490399014307</v>
       </c>
       <c r="U97">
         <f t="shared" si="14"/>
-        <v>1.8434339207750585</v>
+        <v>1.4639215361577109</v>
       </c>
       <c r="W97">
         <f t="shared" si="15"/>
-        <v>127997.48251847885</v>
+        <v>101646.31838497876</v>
       </c>
     </row>
     <row r="98" spans="1:23" x14ac:dyDescent="0.35">
@@ -5402,19 +5406,19 @@
       </c>
       <c r="S98">
         <f t="shared" si="13"/>
-        <v>85.675818764485967</v>
+        <v>48.265222072040906</v>
       </c>
       <c r="T98">
         <f>SUM($S$2:S98)</f>
-        <v>4558.5296182800748</v>
+        <v>4758.3142619734717</v>
       </c>
       <c r="U98">
         <f t="shared" si="14"/>
-        <v>1.7063526107518803</v>
+        <v>1.3866971808424453</v>
       </c>
       <c r="W98">
         <f t="shared" si="15"/>
-        <v>120102.34696601983</v>
+        <v>97603.264941209869</v>
       </c>
     </row>
     <row r="99" spans="1:23" x14ac:dyDescent="0.35">
@@ -5452,19 +5456,19 @@
       </c>
       <c r="S99">
         <f t="shared" si="13"/>
-        <v>10.460825004202349</v>
+        <v>10.525421339416862</v>
       </c>
       <c r="T99">
         <f>SUM($S$2:S99)</f>
-        <v>4568.9904432842768</v>
+        <v>4768.8396833128882</v>
       </c>
       <c r="U99">
         <f t="shared" si="14"/>
-        <v>1.6896152907451572</v>
+        <v>1.3698565066993789</v>
       </c>
       <c r="W99">
         <f t="shared" si="15"/>
-        <v>120538.50179520382</v>
+        <v>97726.655231163895</v>
       </c>
     </row>
     <row r="100" spans="1:23" x14ac:dyDescent="0.35">
@@ -5502,19 +5506,19 @@
       </c>
       <c r="S100">
         <f t="shared" si="13"/>
-        <v>10.301461328763633</v>
+        <v>10.34766954758137</v>
       </c>
       <c r="T100">
         <f>SUM($S$2:S100)</f>
-        <v>4579.2919046130401</v>
+        <v>4779.1873528604692</v>
       </c>
       <c r="U100">
         <f t="shared" si="14"/>
-        <v>1.6731329526191359</v>
+        <v>1.3533002354232493</v>
       </c>
       <c r="W100">
         <f t="shared" si="15"/>
-        <v>120975.64728410498</v>
+        <v>97850.186797036236</v>
       </c>
     </row>
     <row r="101" spans="1:23" x14ac:dyDescent="0.35">
@@ -5556,19 +5560,19 @@
       </c>
       <c r="S101">
         <f>($J$3*N101+$J$4*O101+$J$5*P101+$J$6*Q101+$J$7*R101)*5000</f>
-        <v>210.18461197489978</v>
+        <v>110.21733757596398</v>
       </c>
       <c r="T101">
         <f>SUM($S$2:S101)</f>
-        <v>4789.4765165879398</v>
+        <v>4889.4046904364332</v>
       </c>
       <c r="U101">
         <f t="shared" si="14"/>
-        <v>1.3368375734592963</v>
+        <v>1.176952495301707</v>
       </c>
       <c r="W101">
         <f t="shared" si="15"/>
-        <v>97948.654379148866</v>
+        <v>86234.046283330143</v>
       </c>
     </row>
     <row r="102" spans="1:23" x14ac:dyDescent="0.35">
@@ -5610,19 +5614,19 @@
       </c>
       <c r="S102">
         <f>($J$3*N102+$J$4*O102+$J$5*P102+$J$6*Q102+$J$7*R102)*5000</f>
-        <v>210.09985822629687</v>
+        <v>110.12280454867613</v>
       </c>
       <c r="T102">
         <f>SUM($S$2:S102)</f>
-        <v>4999.5763748142363</v>
+        <v>4999.5274949851091</v>
       </c>
       <c r="U102">
         <f t="shared" si="14"/>
-        <v>1.0006778002972221</v>
+        <v>1.0007560080238254</v>
       </c>
       <c r="W102">
         <f t="shared" si="15"/>
-        <v>74283.306820059006</v>
+        <v>74289.112413576964</v>
       </c>
     </row>
     <row r="103" spans="1:23" x14ac:dyDescent="0.35">
@@ -5647,7 +5651,7 @@
       </c>
       <c r="W104">
         <f>MAX(W2:W102)</f>
-        <v>233259.36872387634</v>
+        <v>231961.35464382442</v>
       </c>
     </row>
     <row r="105" spans="1:23" x14ac:dyDescent="0.35">
